--- a/docs/02_基本設計/02_画面設計書/SCR-303_休暇種別マスタ.xlsx
+++ b/docs/02_基本設計/02_画面設計書/SCR-303_休暇種別マスタ.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -82,8 +82,89 @@
       <color rgb="00C00000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Meiryo"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <color rgb="FFC9D5EE"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <color rgb="FF6B7690"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <color rgb="FF000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <color rgb="FFC00000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <color rgb="FFC00000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <color rgb="FFC0392B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <color rgb="FF1E7B4A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <i val="1"/>
+      <color rgb="FF7F6000"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -115,8 +196,53 @@
         <fgColor rgb="002F75B5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDEDED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B3566"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2F75B5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDECEA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F4EC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="24">
+  <borders count="47">
     <border>
       <left/>
       <right/>
@@ -328,11 +454,198 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <top style="thin">
+        <color rgb="FF8EA9DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="FF8EA9DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF8EA9DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF595959"/>
+      </left>
+      <top style="thin">
+        <color rgb="FF595959"/>
+      </top>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="FF595959"/>
+      </top>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF595959"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF595959"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF595959"/>
+      </left>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF595959"/>
+      </right>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF595959"/>
+      </left>
+      <bottom style="thin">
+        <color rgb="FF595959"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="FF595959"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF595959"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FF595959"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF595959"/>
+      </left>
+      <top style="thin">
+        <color rgb="FF595959"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF595959"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="FF595959"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF595959"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF595959"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF595959"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF595959"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBF9000"/>
+      </left>
+      <top style="thin">
+        <color rgb="FFBF9000"/>
+      </top>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="FFBF9000"/>
+      </top>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FFBF9000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBF9000"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBF9000"/>
+      </left>
+      <bottom style="thin">
+        <color rgb="FFBF9000"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="FFBF9000"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FFBF9000"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FFBF9000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -405,6 +718,126 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -770,7 +1203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:F16"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -782,6 +1215,9 @@
     <col width="3" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="1" t="inlineStr">
         <is>
@@ -790,6 +1226,8 @@
       </c>
     </row>
     <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
         <is>
@@ -801,7 +1239,7 @@
           <t>勤怠フロー</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n"/>
+      <c r="D8" s="38" t="n"/>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
@@ -814,7 +1252,7 @@
           <t>KF-BD-SCR-303</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n"/>
+      <c r="D9" s="38" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
@@ -824,10 +1262,10 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n"/>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="D10" s="38" t="n"/>
     </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
@@ -840,7 +1278,7 @@
           <t>2026/10/03</t>
         </is>
       </c>
-      <c r="D11" s="4" t="n"/>
+      <c r="D11" s="38" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
@@ -853,8 +1291,10 @@
           <t>Wang Sheng</t>
         </is>
       </c>
-      <c r="D12" s="4" t="n"/>
-    </row>
+      <c r="D12" s="38" t="n"/>
+    </row>
+    <row r="13"/>
+    <row r="14"/>
     <row r="15">
       <c r="D15" s="5" t="inlineStr">
         <is>
@@ -901,7 +1341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -960,6 +1400,29 @@
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>実装（AdminLeaveTypeView）に合わせて改訂：一覧＋一覧上のフォームの構成、フォーム項目（名称・法的根拠・有給無給・日数ルール・半日取得・有効無効）、年次有給休暇の固定ルール、実メッセージを追記。削除機能は未実装（無効化で代替）と明記</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -973,7 +1436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1024,7 +1487,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>管理者</t>
+          <t>管理者。ルーターガード：管理者のみ（上長・社員が開くと /home へ戻される）。API は 403（E-010）</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1506,72 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
+          <t>URL（ルート）</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>/admin/leave-types（左メニュー「休暇種別」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>実装</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>frontend/src/views/AdminLeaveTypeView.vue</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>使用API</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>GET /api/admin/leave-types／POST /api/admin/leave-types／PUT /api/admin/leave-types/{id}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
           <t>画面イメージ</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>「画面イメージ」シートを参照（赤い丸数字は項目定義のNoに対応）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>補足</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>一覧と、一覧の上に開く登録・編集フォームで構成する。削除はできず、「有効・無効」を無効にすることで使えなくする。年次有給休暇は名称・有給区分・日数ルール・有効フラグが固定で、変更しようとするとAPIが拒否する（E-016）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>画面構成</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>共通レイアウト（AppLayout）：上部バー（勤怠フロー／通知ベル／氏名／ロール表示／パスワード変更／ログアウト）＋左メニュー（ロール別）＋本文。ベルは未読通知の件数を表示し、画面遷移時と60秒ごとに GET /api/notifications で再取得する（SCR-108）。画面幅900px以下では左メニューは☰ボタンで開閉する。</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BH38"/>
+  <dimension ref="A1:BH42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.6" customWidth="1" min="1" max="1"/>
@@ -1130,1156 +1653,2951 @@
   </cols>
   <sheetData>
     <row r="1" ht="17" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>勤怠フロー</t>
-        </is>
-      </c>
-      <c r="B1" s="10" t="n"/>
-      <c r="C1" s="10" t="n"/>
-      <c r="D1" s="10" t="n"/>
-      <c r="E1" s="10" t="n"/>
-      <c r="F1" s="10" t="n"/>
-      <c r="G1" s="10" t="n"/>
-      <c r="H1" s="10" t="n"/>
-      <c r="I1" s="10" t="n"/>
-      <c r="J1" s="10" t="n"/>
-      <c r="K1" s="10" t="n"/>
-      <c r="L1" s="10" t="n"/>
-      <c r="M1" s="10" t="n"/>
-      <c r="N1" s="10" t="n"/>
-      <c r="O1" s="10" t="n"/>
-      <c r="P1" s="10" t="n"/>
-      <c r="Q1" s="10" t="n"/>
-      <c r="R1" s="10" t="n"/>
-      <c r="S1" s="10" t="n"/>
-      <c r="T1" s="10" t="n"/>
-      <c r="U1" s="10" t="n"/>
-      <c r="V1" s="10" t="n"/>
-      <c r="W1" s="10" t="n"/>
-      <c r="X1" s="10" t="n"/>
-      <c r="Y1" s="10" t="n"/>
-      <c r="Z1" s="10" t="n"/>
-      <c r="AA1" s="10" t="n"/>
-      <c r="AB1" s="10" t="n"/>
-      <c r="AC1" s="10" t="n"/>
-      <c r="AD1" s="10" t="n"/>
-      <c r="AE1" s="10" t="n"/>
-      <c r="AF1" s="10" t="n"/>
-      <c r="AG1" s="10" t="n"/>
-      <c r="AH1" s="10" t="n"/>
-      <c r="AI1" s="10" t="n"/>
-      <c r="AJ1" s="10" t="n"/>
-      <c r="AK1" s="10" t="n"/>
-      <c r="AL1" s="10" t="n"/>
-      <c r="AM1" s="10" t="n"/>
-      <c r="AN1" s="10" t="n"/>
-      <c r="AO1" s="10" t="n"/>
-      <c r="AP1" s="10" t="n"/>
-      <c r="AQ1" s="11" t="n"/>
-      <c r="AR1" s="12" t="inlineStr">
-        <is>
-          <t>Wang Sheng（従業員）  ログアウト</t>
-        </is>
-      </c>
-      <c r="AS1" s="10" t="n"/>
-      <c r="AT1" s="10" t="n"/>
-      <c r="AU1" s="10" t="n"/>
-      <c r="AV1" s="10" t="n"/>
-      <c r="AW1" s="10" t="n"/>
-      <c r="AX1" s="10" t="n"/>
-      <c r="AY1" s="10" t="n"/>
-      <c r="AZ1" s="10" t="n"/>
-      <c r="BA1" s="10" t="n"/>
-      <c r="BB1" s="10" t="n"/>
-      <c r="BC1" s="10" t="n"/>
-      <c r="BD1" s="10" t="n"/>
-      <c r="BE1" s="10" t="n"/>
-      <c r="BF1" s="10" t="n"/>
-      <c r="BG1" s="10" t="n"/>
-      <c r="BH1" s="11" t="n"/>
+      <c r="A1" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  勤怠フロー</t>
+        </is>
+      </c>
+      <c r="B1" s="40" t="n"/>
+      <c r="C1" s="40" t="n"/>
+      <c r="D1" s="40" t="n"/>
+      <c r="E1" s="40" t="n"/>
+      <c r="F1" s="40" t="n"/>
+      <c r="G1" s="40" t="n"/>
+      <c r="H1" s="40" t="n"/>
+      <c r="I1" s="40" t="n"/>
+      <c r="J1" s="40" t="n"/>
+      <c r="K1" s="40" t="n"/>
+      <c r="L1" s="40" t="n"/>
+      <c r="M1" s="40" t="n"/>
+      <c r="N1" s="40" t="n"/>
+      <c r="O1" s="41" t="n"/>
+      <c r="P1" s="41" t="n"/>
+      <c r="Q1" s="41" t="n"/>
+      <c r="R1" s="41" t="n"/>
+      <c r="S1" s="41" t="n"/>
+      <c r="T1" s="41" t="n"/>
+      <c r="U1" s="41" t="n"/>
+      <c r="V1" s="41" t="n"/>
+      <c r="W1" s="41" t="n"/>
+      <c r="X1" s="41" t="n"/>
+      <c r="Y1" s="41" t="n"/>
+      <c r="Z1" s="41" t="n"/>
+      <c r="AA1" s="41" t="n"/>
+      <c r="AB1" s="41" t="n"/>
+      <c r="AC1" s="41" t="n"/>
+      <c r="AD1" s="41" t="n"/>
+      <c r="AE1" s="41" t="n"/>
+      <c r="AF1" s="41" t="n"/>
+      <c r="AG1" s="41" t="n"/>
+      <c r="AH1" s="42" t="inlineStr">
+        <is>
+          <t>🔔 3</t>
+        </is>
+      </c>
+      <c r="AI1" s="40" t="n"/>
+      <c r="AJ1" s="40" t="n"/>
+      <c r="AK1" s="40" t="n"/>
+      <c r="AL1" s="42" t="inlineStr">
+        <is>
+          <t>Wang Sheng  [管理者]</t>
+        </is>
+      </c>
+      <c r="AM1" s="40" t="n"/>
+      <c r="AN1" s="40" t="n"/>
+      <c r="AO1" s="40" t="n"/>
+      <c r="AP1" s="40" t="n"/>
+      <c r="AQ1" s="40" t="n"/>
+      <c r="AR1" s="40" t="n"/>
+      <c r="AS1" s="40" t="n"/>
+      <c r="AT1" s="40" t="n"/>
+      <c r="AU1" s="40" t="n"/>
+      <c r="AV1" s="43" t="inlineStr">
+        <is>
+          <t>パスワード変更</t>
+        </is>
+      </c>
+      <c r="AW1" s="40" t="n"/>
+      <c r="AX1" s="40" t="n"/>
+      <c r="AY1" s="40" t="n"/>
+      <c r="AZ1" s="40" t="n"/>
+      <c r="BA1" s="40" t="n"/>
+      <c r="BB1" s="41" t="n"/>
+      <c r="BC1" s="41" t="n"/>
+      <c r="BD1" s="41" t="n"/>
+      <c r="BE1" s="41" t="n"/>
+      <c r="BF1" s="41" t="n"/>
+      <c r="BG1" s="41" t="n"/>
+      <c r="BH1" s="41" t="n"/>
     </row>
     <row r="2" ht="17" customHeight="1">
-      <c r="A2" s="13" t="n"/>
-      <c r="AQ2" s="14" t="n"/>
-      <c r="AR2" s="13" t="n"/>
-      <c r="BH2" s="14" t="n"/>
+      <c r="A2" s="40" t="n"/>
+      <c r="B2" s="40" t="n"/>
+      <c r="C2" s="40" t="n"/>
+      <c r="D2" s="40" t="n"/>
+      <c r="E2" s="40" t="n"/>
+      <c r="F2" s="40" t="n"/>
+      <c r="G2" s="40" t="n"/>
+      <c r="H2" s="40" t="n"/>
+      <c r="I2" s="40" t="n"/>
+      <c r="J2" s="40" t="n"/>
+      <c r="K2" s="40" t="n"/>
+      <c r="L2" s="40" t="n"/>
+      <c r="M2" s="40" t="n"/>
+      <c r="N2" s="40" t="n"/>
+      <c r="O2" s="41" t="n"/>
+      <c r="P2" s="41" t="n"/>
+      <c r="Q2" s="41" t="n"/>
+      <c r="R2" s="41" t="n"/>
+      <c r="S2" s="41" t="n"/>
+      <c r="T2" s="41" t="n"/>
+      <c r="U2" s="41" t="n"/>
+      <c r="V2" s="41" t="n"/>
+      <c r="W2" s="41" t="n"/>
+      <c r="X2" s="41" t="n"/>
+      <c r="Y2" s="41" t="n"/>
+      <c r="Z2" s="41" t="n"/>
+      <c r="AA2" s="41" t="n"/>
+      <c r="AB2" s="41" t="n"/>
+      <c r="AC2" s="41" t="n"/>
+      <c r="AD2" s="41" t="n"/>
+      <c r="AE2" s="41" t="n"/>
+      <c r="AF2" s="41" t="n"/>
+      <c r="AG2" s="41" t="n"/>
+      <c r="AH2" s="40" t="n"/>
+      <c r="AI2" s="40" t="n"/>
+      <c r="AJ2" s="40" t="n"/>
+      <c r="AK2" s="40" t="n"/>
+      <c r="AL2" s="40" t="n"/>
+      <c r="AM2" s="40" t="n"/>
+      <c r="AN2" s="40" t="n"/>
+      <c r="AO2" s="40" t="n"/>
+      <c r="AP2" s="40" t="n"/>
+      <c r="AQ2" s="40" t="n"/>
+      <c r="AR2" s="40" t="n"/>
+      <c r="AS2" s="40" t="n"/>
+      <c r="AT2" s="40" t="n"/>
+      <c r="AU2" s="40" t="n"/>
+      <c r="AV2" s="40" t="n"/>
+      <c r="AW2" s="40" t="n"/>
+      <c r="AX2" s="40" t="n"/>
+      <c r="AY2" s="40" t="n"/>
+      <c r="AZ2" s="40" t="n"/>
+      <c r="BA2" s="40" t="n"/>
+      <c r="BB2" s="44" t="inlineStr">
+        <is>
+          <t>ログアウト</t>
+        </is>
+      </c>
+      <c r="BC2" s="45" t="n"/>
+      <c r="BD2" s="45" t="n"/>
+      <c r="BE2" s="45" t="n"/>
+      <c r="BF2" s="45" t="n"/>
+      <c r="BG2" s="46" t="n"/>
+      <c r="BH2" s="41" t="n"/>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="15" t="n"/>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n"/>
-      <c r="D3" s="16" t="n"/>
-      <c r="E3" s="16" t="n"/>
-      <c r="F3" s="16" t="n"/>
-      <c r="G3" s="16" t="n"/>
-      <c r="H3" s="16" t="n"/>
-      <c r="I3" s="16" t="n"/>
-      <c r="J3" s="16" t="n"/>
-      <c r="K3" s="16" t="n"/>
-      <c r="L3" s="16" t="n"/>
-      <c r="M3" s="16" t="n"/>
-      <c r="N3" s="16" t="n"/>
-      <c r="O3" s="16" t="n"/>
-      <c r="P3" s="16" t="n"/>
-      <c r="Q3" s="16" t="n"/>
-      <c r="R3" s="16" t="n"/>
-      <c r="S3" s="16" t="n"/>
-      <c r="T3" s="16" t="n"/>
-      <c r="U3" s="16" t="n"/>
-      <c r="V3" s="16" t="n"/>
-      <c r="W3" s="16" t="n"/>
-      <c r="X3" s="16" t="n"/>
-      <c r="Y3" s="16" t="n"/>
-      <c r="Z3" s="16" t="n"/>
-      <c r="AA3" s="16" t="n"/>
-      <c r="AB3" s="16" t="n"/>
-      <c r="AC3" s="16" t="n"/>
-      <c r="AD3" s="16" t="n"/>
-      <c r="AE3" s="16" t="n"/>
-      <c r="AF3" s="16" t="n"/>
-      <c r="AG3" s="16" t="n"/>
-      <c r="AH3" s="16" t="n"/>
-      <c r="AI3" s="16" t="n"/>
-      <c r="AJ3" s="16" t="n"/>
-      <c r="AK3" s="16" t="n"/>
-      <c r="AL3" s="16" t="n"/>
-      <c r="AM3" s="16" t="n"/>
-      <c r="AN3" s="16" t="n"/>
-      <c r="AO3" s="16" t="n"/>
-      <c r="AP3" s="16" t="n"/>
-      <c r="AQ3" s="17" t="n"/>
-      <c r="AR3" s="15" t="n"/>
-      <c r="AS3" s="16" t="n"/>
-      <c r="AT3" s="16" t="n"/>
-      <c r="AU3" s="16" t="n"/>
-      <c r="AV3" s="16" t="n"/>
-      <c r="AW3" s="16" t="n"/>
-      <c r="AX3" s="16" t="n"/>
-      <c r="AY3" s="16" t="n"/>
-      <c r="AZ3" s="16" t="n"/>
-      <c r="BA3" s="16" t="n"/>
-      <c r="BB3" s="16" t="n"/>
-      <c r="BC3" s="16" t="n"/>
-      <c r="BD3" s="16" t="n"/>
-      <c r="BE3" s="16" t="n"/>
-      <c r="BF3" s="16" t="n"/>
-      <c r="BG3" s="16" t="n"/>
-      <c r="BH3" s="17" t="n"/>
-    </row>
-    <row r="4" ht="17" customHeight="1"/>
+      <c r="A3" s="40" t="n"/>
+      <c r="B3" s="40" t="n"/>
+      <c r="C3" s="40" t="n"/>
+      <c r="D3" s="40" t="n"/>
+      <c r="E3" s="40" t="n"/>
+      <c r="F3" s="40" t="n"/>
+      <c r="G3" s="40" t="n"/>
+      <c r="H3" s="40" t="n"/>
+      <c r="I3" s="40" t="n"/>
+      <c r="J3" s="40" t="n"/>
+      <c r="K3" s="40" t="n"/>
+      <c r="L3" s="40" t="n"/>
+      <c r="M3" s="40" t="n"/>
+      <c r="N3" s="40" t="n"/>
+      <c r="O3" s="41" t="n"/>
+      <c r="P3" s="41" t="n"/>
+      <c r="Q3" s="41" t="n"/>
+      <c r="R3" s="41" t="n"/>
+      <c r="S3" s="41" t="n"/>
+      <c r="T3" s="41" t="n"/>
+      <c r="U3" s="41" t="n"/>
+      <c r="V3" s="41" t="n"/>
+      <c r="W3" s="41" t="n"/>
+      <c r="X3" s="41" t="n"/>
+      <c r="Y3" s="41" t="n"/>
+      <c r="Z3" s="41" t="n"/>
+      <c r="AA3" s="41" t="n"/>
+      <c r="AB3" s="41" t="n"/>
+      <c r="AC3" s="41" t="n"/>
+      <c r="AD3" s="41" t="n"/>
+      <c r="AE3" s="41" t="n"/>
+      <c r="AF3" s="41" t="n"/>
+      <c r="AG3" s="41" t="n"/>
+      <c r="AH3" s="40" t="n"/>
+      <c r="AI3" s="40" t="n"/>
+      <c r="AJ3" s="40" t="n"/>
+      <c r="AK3" s="40" t="n"/>
+      <c r="AL3" s="40" t="n"/>
+      <c r="AM3" s="40" t="n"/>
+      <c r="AN3" s="40" t="n"/>
+      <c r="AO3" s="40" t="n"/>
+      <c r="AP3" s="40" t="n"/>
+      <c r="AQ3" s="40" t="n"/>
+      <c r="AR3" s="40" t="n"/>
+      <c r="AS3" s="40" t="n"/>
+      <c r="AT3" s="40" t="n"/>
+      <c r="AU3" s="40" t="n"/>
+      <c r="AV3" s="40" t="n"/>
+      <c r="AW3" s="40" t="n"/>
+      <c r="AX3" s="40" t="n"/>
+      <c r="AY3" s="40" t="n"/>
+      <c r="AZ3" s="40" t="n"/>
+      <c r="BA3" s="40" t="n"/>
+      <c r="BB3" s="41" t="n"/>
+      <c r="BC3" s="41" t="n"/>
+      <c r="BD3" s="41" t="n"/>
+      <c r="BE3" s="41" t="n"/>
+      <c r="BF3" s="41" t="n"/>
+      <c r="BG3" s="41" t="n"/>
+      <c r="BH3" s="41" t="n"/>
+    </row>
+    <row r="4" ht="17" customHeight="1">
+      <c r="A4" s="47" t="n"/>
+      <c r="B4" s="47" t="n"/>
+      <c r="C4" s="47" t="n"/>
+      <c r="D4" s="47" t="n"/>
+      <c r="E4" s="47" t="n"/>
+      <c r="F4" s="47" t="n"/>
+      <c r="G4" s="47" t="n"/>
+      <c r="H4" s="47" t="n"/>
+      <c r="I4" s="47" t="n"/>
+      <c r="J4" s="47" t="n"/>
+      <c r="K4" s="47" t="n"/>
+      <c r="L4" s="47" t="n"/>
+      <c r="M4" s="47" t="n"/>
+      <c r="N4" s="47" t="n"/>
+      <c r="O4" s="47" t="n"/>
+      <c r="P4" s="47" t="n"/>
+      <c r="Q4" s="47" t="n"/>
+      <c r="R4" s="47" t="n"/>
+      <c r="S4" s="47" t="n"/>
+      <c r="T4" s="47" t="n"/>
+      <c r="U4" s="47" t="n"/>
+      <c r="V4" s="47" t="n"/>
+      <c r="W4" s="47" t="n"/>
+      <c r="X4" s="47" t="n"/>
+      <c r="Y4" s="47" t="n"/>
+      <c r="Z4" s="47" t="n"/>
+      <c r="AA4" s="47" t="n"/>
+      <c r="AB4" s="47" t="n"/>
+      <c r="AC4" s="47" t="n"/>
+      <c r="AD4" s="47" t="n"/>
+      <c r="AE4" s="47" t="n"/>
+      <c r="AF4" s="47" t="n"/>
+      <c r="AG4" s="47" t="n"/>
+      <c r="AH4" s="47" t="n"/>
+      <c r="AI4" s="47" t="n"/>
+      <c r="AJ4" s="47" t="n"/>
+      <c r="AK4" s="47" t="n"/>
+      <c r="AL4" s="47" t="n"/>
+      <c r="AM4" s="47" t="n"/>
+      <c r="AN4" s="47" t="n"/>
+      <c r="AO4" s="47" t="n"/>
+      <c r="AP4" s="47" t="n"/>
+      <c r="AQ4" s="47" t="n"/>
+      <c r="AR4" s="47" t="n"/>
+      <c r="AS4" s="47" t="n"/>
+      <c r="AT4" s="47" t="n"/>
+      <c r="AU4" s="47" t="n"/>
+      <c r="AV4" s="47" t="n"/>
+      <c r="AW4" s="47" t="n"/>
+      <c r="AX4" s="47" t="n"/>
+      <c r="AY4" s="47" t="n"/>
+      <c r="AZ4" s="47" t="n"/>
+      <c r="BA4" s="47" t="n"/>
+      <c r="BB4" s="47" t="n"/>
+      <c r="BC4" s="47" t="n"/>
+      <c r="BD4" s="47" t="n"/>
+      <c r="BE4" s="47" t="n"/>
+      <c r="BF4" s="47" t="n"/>
+      <c r="BG4" s="47" t="n"/>
+      <c r="BH4" s="47" t="n"/>
+    </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="18" t="inlineStr"/>
-      <c r="B5" s="19" t="n"/>
-      <c r="C5" s="19" t="n"/>
-      <c r="D5" s="19" t="n"/>
-      <c r="E5" s="19" t="n"/>
-      <c r="F5" s="19" t="n"/>
-      <c r="G5" s="19" t="n"/>
-      <c r="H5" s="19" t="n"/>
-      <c r="I5" s="19" t="n"/>
-      <c r="J5" s="19" t="n"/>
-      <c r="K5" s="19" t="n"/>
-      <c r="L5" s="20" t="n"/>
-      <c r="N5" s="21" t="inlineStr">
-        <is>
-          <t>休暇種別マスタ</t>
-        </is>
-      </c>
+      <c r="A5" s="48" t="n"/>
+      <c r="B5" s="49" t="n"/>
+      <c r="C5" s="49" t="n"/>
+      <c r="D5" s="49" t="n"/>
+      <c r="E5" s="49" t="n"/>
+      <c r="F5" s="49" t="n"/>
+      <c r="G5" s="49" t="n"/>
+      <c r="H5" s="49" t="n"/>
+      <c r="I5" s="49" t="n"/>
+      <c r="J5" s="49" t="n"/>
+      <c r="K5" s="49" t="n"/>
+      <c r="L5" s="50" t="n"/>
+      <c r="M5" s="47" t="n"/>
+      <c r="N5" s="51" t="inlineStr">
+        <is>
+          <t>休暇種別</t>
+        </is>
+      </c>
+      <c r="AE5" s="47" t="n"/>
+      <c r="AF5" s="47" t="n"/>
+      <c r="AG5" s="47" t="n"/>
+      <c r="AH5" s="47" t="n"/>
+      <c r="AI5" s="47" t="n"/>
+      <c r="AJ5" s="47" t="n"/>
+      <c r="AK5" s="47" t="n"/>
+      <c r="AL5" s="47" t="n"/>
+      <c r="AM5" s="47" t="n"/>
+      <c r="AN5" s="47" t="n"/>
+      <c r="AO5" s="47" t="n"/>
+      <c r="AP5" s="47" t="n"/>
+      <c r="AQ5" s="47" t="n"/>
+      <c r="AR5" s="47" t="n"/>
+      <c r="AS5" s="47" t="n"/>
+      <c r="AT5" s="47" t="n"/>
+      <c r="AU5" s="47" t="n"/>
+      <c r="AV5" s="52" t="inlineStr">
+        <is>
+          <t>新規登録</t>
+        </is>
+      </c>
+      <c r="AW5" s="53" t="n"/>
+      <c r="AX5" s="53" t="n"/>
+      <c r="AY5" s="53" t="n"/>
+      <c r="AZ5" s="53" t="n"/>
+      <c r="BA5" s="53" t="n"/>
+      <c r="BB5" s="53" t="n"/>
+      <c r="BC5" s="53" t="n"/>
+      <c r="BD5" s="53" t="n"/>
+      <c r="BE5" s="53" t="n"/>
+      <c r="BF5" s="54" t="n"/>
+      <c r="BG5" s="47" t="n"/>
+      <c r="BH5" s="47" t="n"/>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="22" t="n"/>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t>ホーム</t>
-        </is>
-      </c>
-      <c r="L6" s="24" t="n"/>
+      <c r="A6" s="55" t="n"/>
+      <c r="B6" s="56" t="inlineStr">
+        <is>
+          <t>勤怠</t>
+        </is>
+      </c>
+      <c r="C6" s="57" t="n"/>
+      <c r="D6" s="57" t="n"/>
+      <c r="E6" s="57" t="n"/>
+      <c r="F6" s="57" t="n"/>
+      <c r="G6" s="57" t="n"/>
+      <c r="H6" s="57" t="n"/>
+      <c r="I6" s="57" t="n"/>
+      <c r="J6" s="57" t="n"/>
+      <c r="K6" s="57" t="n"/>
+      <c r="L6" s="58" t="n"/>
+      <c r="M6" s="47" t="n"/>
+      <c r="AE6" s="47" t="n"/>
+      <c r="AF6" s="47" t="n"/>
+      <c r="AG6" s="47" t="n"/>
+      <c r="AH6" s="47" t="n"/>
+      <c r="AI6" s="47" t="n"/>
+      <c r="AJ6" s="47" t="n"/>
+      <c r="AK6" s="47" t="n"/>
+      <c r="AL6" s="47" t="n"/>
+      <c r="AM6" s="47" t="n"/>
+      <c r="AN6" s="47" t="n"/>
+      <c r="AO6" s="47" t="n"/>
+      <c r="AP6" s="47" t="n"/>
+      <c r="AQ6" s="47" t="n"/>
+      <c r="AR6" s="47" t="n"/>
+      <c r="AS6" s="47" t="n"/>
+      <c r="AT6" s="47" t="n"/>
+      <c r="AU6" s="59" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="AV6" s="60" t="n"/>
+      <c r="AW6" s="61" t="n"/>
+      <c r="AX6" s="61" t="n"/>
+      <c r="AY6" s="61" t="n"/>
+      <c r="AZ6" s="61" t="n"/>
+      <c r="BA6" s="61" t="n"/>
+      <c r="BB6" s="61" t="n"/>
+      <c r="BC6" s="61" t="n"/>
+      <c r="BD6" s="61" t="n"/>
+      <c r="BE6" s="61" t="n"/>
+      <c r="BF6" s="62" t="n"/>
+      <c r="BG6" s="47" t="n"/>
+      <c r="BH6" s="47" t="n"/>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="22" t="n"/>
-      <c r="L7" s="24" t="n"/>
+      <c r="A7" s="55" t="n"/>
+      <c r="B7" s="63" t="inlineStr">
+        <is>
+          <t>打刻・勤怠</t>
+        </is>
+      </c>
+      <c r="C7" s="57" t="n"/>
+      <c r="D7" s="57" t="n"/>
+      <c r="E7" s="57" t="n"/>
+      <c r="F7" s="57" t="n"/>
+      <c r="G7" s="57" t="n"/>
+      <c r="H7" s="57" t="n"/>
+      <c r="I7" s="57" t="n"/>
+      <c r="J7" s="57" t="n"/>
+      <c r="K7" s="57" t="n"/>
+      <c r="L7" s="58" t="n"/>
+      <c r="M7" s="47" t="n"/>
+      <c r="N7" s="47" t="n"/>
+      <c r="O7" s="47" t="n"/>
+      <c r="P7" s="47" t="n"/>
+      <c r="Q7" s="47" t="n"/>
+      <c r="R7" s="47" t="n"/>
+      <c r="S7" s="47" t="n"/>
+      <c r="T7" s="47" t="n"/>
+      <c r="U7" s="47" t="n"/>
+      <c r="V7" s="47" t="n"/>
+      <c r="W7" s="47" t="n"/>
+      <c r="X7" s="47" t="n"/>
+      <c r="Y7" s="47" t="n"/>
+      <c r="Z7" s="47" t="n"/>
+      <c r="AA7" s="47" t="n"/>
+      <c r="AB7" s="47" t="n"/>
+      <c r="AC7" s="47" t="n"/>
+      <c r="AD7" s="47" t="n"/>
+      <c r="AE7" s="47" t="n"/>
+      <c r="AF7" s="47" t="n"/>
+      <c r="AG7" s="47" t="n"/>
+      <c r="AH7" s="47" t="n"/>
+      <c r="AI7" s="47" t="n"/>
+      <c r="AJ7" s="47" t="n"/>
+      <c r="AK7" s="47" t="n"/>
+      <c r="AL7" s="47" t="n"/>
+      <c r="AM7" s="47" t="n"/>
+      <c r="AN7" s="47" t="n"/>
+      <c r="AO7" s="47" t="n"/>
+      <c r="AP7" s="47" t="n"/>
+      <c r="AQ7" s="47" t="n"/>
+      <c r="AR7" s="47" t="n"/>
+      <c r="AS7" s="47" t="n"/>
+      <c r="AT7" s="47" t="n"/>
+      <c r="AU7" s="47" t="n"/>
+      <c r="AV7" s="47" t="n"/>
+      <c r="AW7" s="47" t="n"/>
+      <c r="AX7" s="47" t="n"/>
+      <c r="AY7" s="47" t="n"/>
+      <c r="AZ7" s="47" t="n"/>
+      <c r="BA7" s="47" t="n"/>
+      <c r="BB7" s="47" t="n"/>
+      <c r="BC7" s="47" t="n"/>
+      <c r="BD7" s="47" t="n"/>
+      <c r="BE7" s="47" t="n"/>
+      <c r="BF7" s="47" t="n"/>
+      <c r="BG7" s="47" t="n"/>
+      <c r="BH7" s="47" t="n"/>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="22" t="n"/>
-      <c r="B8" s="23" t="inlineStr">
-        <is>
-          <t>打刻</t>
-        </is>
-      </c>
-      <c r="L8" s="24" t="n"/>
-      <c r="M8" s="25" t="inlineStr">
-        <is>
-          <t>①</t>
-        </is>
-      </c>
-      <c r="N8" s="26" t="inlineStr">
+      <c r="A8" s="55" t="n"/>
+      <c r="B8" s="57" t="n"/>
+      <c r="C8" s="57" t="n"/>
+      <c r="D8" s="57" t="n"/>
+      <c r="E8" s="57" t="n"/>
+      <c r="F8" s="57" t="n"/>
+      <c r="G8" s="57" t="n"/>
+      <c r="H8" s="57" t="n"/>
+      <c r="I8" s="57" t="n"/>
+      <c r="J8" s="57" t="n"/>
+      <c r="K8" s="57" t="n"/>
+      <c r="L8" s="58" t="n"/>
+      <c r="M8" s="47" t="n"/>
+      <c r="N8" s="64" t="n"/>
+      <c r="O8" s="65" t="n"/>
+      <c r="P8" s="65" t="n"/>
+      <c r="Q8" s="65" t="n"/>
+      <c r="R8" s="65" t="n"/>
+      <c r="S8" s="65" t="n"/>
+      <c r="T8" s="65" t="n"/>
+      <c r="U8" s="65" t="n"/>
+      <c r="V8" s="65" t="n"/>
+      <c r="W8" s="65" t="n"/>
+      <c r="X8" s="65" t="n"/>
+      <c r="Y8" s="65" t="n"/>
+      <c r="Z8" s="65" t="n"/>
+      <c r="AA8" s="65" t="n"/>
+      <c r="AB8" s="65" t="n"/>
+      <c r="AC8" s="65" t="n"/>
+      <c r="AD8" s="65" t="n"/>
+      <c r="AE8" s="65" t="n"/>
+      <c r="AF8" s="65" t="n"/>
+      <c r="AG8" s="65" t="n"/>
+      <c r="AH8" s="65" t="n"/>
+      <c r="AI8" s="65" t="n"/>
+      <c r="AJ8" s="65" t="n"/>
+      <c r="AK8" s="65" t="n"/>
+      <c r="AL8" s="65" t="n"/>
+      <c r="AM8" s="65" t="n"/>
+      <c r="AN8" s="65" t="n"/>
+      <c r="AO8" s="65" t="n"/>
+      <c r="AP8" s="65" t="n"/>
+      <c r="AQ8" s="65" t="n"/>
+      <c r="AR8" s="65" t="n"/>
+      <c r="AS8" s="65" t="n"/>
+      <c r="AT8" s="65" t="n"/>
+      <c r="AU8" s="65" t="n"/>
+      <c r="AV8" s="65" t="n"/>
+      <c r="AW8" s="65" t="n"/>
+      <c r="AX8" s="65" t="n"/>
+      <c r="AY8" s="65" t="n"/>
+      <c r="AZ8" s="65" t="n"/>
+      <c r="BA8" s="65" t="n"/>
+      <c r="BB8" s="65" t="n"/>
+      <c r="BC8" s="65" t="n"/>
+      <c r="BD8" s="65" t="n"/>
+      <c r="BE8" s="65" t="n"/>
+      <c r="BF8" s="66" t="n"/>
+      <c r="BG8" s="47" t="n"/>
+      <c r="BH8" s="47" t="n"/>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="55" t="n"/>
+      <c r="B9" s="63" t="inlineStr">
+        <is>
+          <t>申請</t>
+        </is>
+      </c>
+      <c r="C9" s="57" t="n"/>
+      <c r="D9" s="57" t="n"/>
+      <c r="E9" s="57" t="n"/>
+      <c r="F9" s="57" t="n"/>
+      <c r="G9" s="57" t="n"/>
+      <c r="H9" s="57" t="n"/>
+      <c r="I9" s="57" t="n"/>
+      <c r="J9" s="57" t="n"/>
+      <c r="K9" s="57" t="n"/>
+      <c r="L9" s="58" t="n"/>
+      <c r="M9" s="47" t="n"/>
+      <c r="N9" s="67" t="n"/>
+      <c r="O9" s="68" t="n"/>
+      <c r="P9" s="69" t="inlineStr">
+        <is>
+          <t>休暇種別の新規登録（編集）</t>
+        </is>
+      </c>
+      <c r="Q9" s="70" t="n"/>
+      <c r="R9" s="70" t="n"/>
+      <c r="S9" s="70" t="n"/>
+      <c r="T9" s="70" t="n"/>
+      <c r="U9" s="70" t="n"/>
+      <c r="V9" s="70" t="n"/>
+      <c r="W9" s="70" t="n"/>
+      <c r="X9" s="70" t="n"/>
+      <c r="Y9" s="70" t="n"/>
+      <c r="Z9" s="70" t="n"/>
+      <c r="AA9" s="70" t="n"/>
+      <c r="AB9" s="70" t="n"/>
+      <c r="AC9" s="70" t="n"/>
+      <c r="AD9" s="70" t="n"/>
+      <c r="AE9" s="68" t="n"/>
+      <c r="AF9" s="68" t="n"/>
+      <c r="AG9" s="68" t="n"/>
+      <c r="AH9" s="68" t="n"/>
+      <c r="AI9" s="68" t="n"/>
+      <c r="AJ9" s="68" t="n"/>
+      <c r="AK9" s="68" t="n"/>
+      <c r="AL9" s="68" t="n"/>
+      <c r="AM9" s="68" t="n"/>
+      <c r="AN9" s="68" t="n"/>
+      <c r="AO9" s="68" t="n"/>
+      <c r="AP9" s="68" t="n"/>
+      <c r="AQ9" s="68" t="n"/>
+      <c r="AR9" s="68" t="n"/>
+      <c r="AS9" s="68" t="n"/>
+      <c r="AT9" s="68" t="n"/>
+      <c r="AU9" s="68" t="n"/>
+      <c r="AV9" s="68" t="n"/>
+      <c r="AW9" s="68" t="n"/>
+      <c r="AX9" s="68" t="n"/>
+      <c r="AY9" s="68" t="n"/>
+      <c r="AZ9" s="68" t="n"/>
+      <c r="BA9" s="68" t="n"/>
+      <c r="BB9" s="68" t="n"/>
+      <c r="BC9" s="68" t="n"/>
+      <c r="BD9" s="68" t="n"/>
+      <c r="BE9" s="68" t="n"/>
+      <c r="BF9" s="71" t="n"/>
+      <c r="BG9" s="47" t="n"/>
+      <c r="BH9" s="47" t="n"/>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="55" t="n"/>
+      <c r="B10" s="57" t="n"/>
+      <c r="C10" s="57" t="n"/>
+      <c r="D10" s="57" t="n"/>
+      <c r="E10" s="57" t="n"/>
+      <c r="F10" s="57" t="n"/>
+      <c r="G10" s="57" t="n"/>
+      <c r="H10" s="57" t="n"/>
+      <c r="I10" s="57" t="n"/>
+      <c r="J10" s="57" t="n"/>
+      <c r="K10" s="57" t="n"/>
+      <c r="L10" s="58" t="n"/>
+      <c r="M10" s="47" t="n"/>
+      <c r="N10" s="67" t="n"/>
+      <c r="O10" s="68" t="n"/>
+      <c r="P10" s="68" t="n"/>
+      <c r="Q10" s="68" t="n"/>
+      <c r="R10" s="68" t="n"/>
+      <c r="S10" s="68" t="n"/>
+      <c r="T10" s="68" t="n"/>
+      <c r="U10" s="68" t="n"/>
+      <c r="V10" s="68" t="n"/>
+      <c r="W10" s="68" t="n"/>
+      <c r="X10" s="68" t="n"/>
+      <c r="Y10" s="68" t="n"/>
+      <c r="Z10" s="68" t="n"/>
+      <c r="AA10" s="68" t="n"/>
+      <c r="AB10" s="68" t="n"/>
+      <c r="AC10" s="68" t="n"/>
+      <c r="AD10" s="68" t="n"/>
+      <c r="AE10" s="68" t="n"/>
+      <c r="AF10" s="68" t="n"/>
+      <c r="AG10" s="68" t="n"/>
+      <c r="AH10" s="68" t="n"/>
+      <c r="AI10" s="68" t="n"/>
+      <c r="AJ10" s="68" t="n"/>
+      <c r="AK10" s="68" t="n"/>
+      <c r="AL10" s="68" t="n"/>
+      <c r="AM10" s="68" t="n"/>
+      <c r="AN10" s="68" t="n"/>
+      <c r="AO10" s="68" t="n"/>
+      <c r="AP10" s="68" t="n"/>
+      <c r="AQ10" s="68" t="n"/>
+      <c r="AR10" s="68" t="n"/>
+      <c r="AS10" s="68" t="n"/>
+      <c r="AT10" s="68" t="n"/>
+      <c r="AU10" s="68" t="n"/>
+      <c r="AV10" s="68" t="n"/>
+      <c r="AW10" s="68" t="n"/>
+      <c r="AX10" s="68" t="n"/>
+      <c r="AY10" s="68" t="n"/>
+      <c r="AZ10" s="68" t="n"/>
+      <c r="BA10" s="68" t="n"/>
+      <c r="BB10" s="68" t="n"/>
+      <c r="BC10" s="68" t="n"/>
+      <c r="BD10" s="68" t="n"/>
+      <c r="BE10" s="68" t="n"/>
+      <c r="BF10" s="71" t="n"/>
+      <c r="BG10" s="47" t="n"/>
+      <c r="BH10" s="47" t="n"/>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="55" t="n"/>
+      <c r="B11" s="63" t="inlineStr">
+        <is>
+          <t>休暇残日数</t>
+        </is>
+      </c>
+      <c r="C11" s="57" t="n"/>
+      <c r="D11" s="57" t="n"/>
+      <c r="E11" s="57" t="n"/>
+      <c r="F11" s="57" t="n"/>
+      <c r="G11" s="57" t="n"/>
+      <c r="H11" s="57" t="n"/>
+      <c r="I11" s="57" t="n"/>
+      <c r="J11" s="57" t="n"/>
+      <c r="K11" s="57" t="n"/>
+      <c r="L11" s="58" t="n"/>
+      <c r="M11" s="47" t="n"/>
+      <c r="N11" s="72" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="O11" s="73" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="O8" s="27" t="n"/>
-      <c r="P8" s="27" t="n"/>
-      <c r="Q8" s="27" t="n"/>
-      <c r="R8" s="27" t="n"/>
-      <c r="S8" s="27" t="n"/>
-      <c r="T8" s="27" t="n"/>
-      <c r="U8" s="28" t="n"/>
-      <c r="V8" s="26" t="inlineStr">
+      <c r="P11" s="74" t="n"/>
+      <c r="Q11" s="74" t="n"/>
+      <c r="R11" s="74" t="n"/>
+      <c r="S11" s="74" t="n"/>
+      <c r="T11" s="75" t="n"/>
+      <c r="U11" s="76" t="n"/>
+      <c r="V11" s="77" t="n"/>
+      <c r="W11" s="77" t="n"/>
+      <c r="X11" s="77" t="n"/>
+      <c r="Y11" s="77" t="n"/>
+      <c r="Z11" s="77" t="n"/>
+      <c r="AA11" s="77" t="n"/>
+      <c r="AB11" s="77" t="n"/>
+      <c r="AC11" s="77" t="n"/>
+      <c r="AD11" s="77" t="n"/>
+      <c r="AE11" s="77" t="n"/>
+      <c r="AF11" s="78" t="n"/>
+      <c r="AG11" s="68" t="n"/>
+      <c r="AH11" s="68" t="n"/>
+      <c r="AI11" s="79" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="AJ11" s="73" t="inlineStr">
         <is>
           <t>法的根拠</t>
         </is>
       </c>
-      <c r="W8" s="27" t="n"/>
-      <c r="X8" s="27" t="n"/>
-      <c r="Y8" s="27" t="n"/>
-      <c r="Z8" s="27" t="n"/>
-      <c r="AA8" s="27" t="n"/>
-      <c r="AB8" s="27" t="n"/>
-      <c r="AC8" s="28" t="n"/>
-      <c r="AD8" s="26" t="inlineStr">
+      <c r="AK11" s="74" t="n"/>
+      <c r="AL11" s="74" t="n"/>
+      <c r="AM11" s="74" t="n"/>
+      <c r="AN11" s="74" t="n"/>
+      <c r="AO11" s="75" t="n"/>
+      <c r="AP11" s="76" t="n"/>
+      <c r="AQ11" s="77" t="n"/>
+      <c r="AR11" s="77" t="n"/>
+      <c r="AS11" s="77" t="n"/>
+      <c r="AT11" s="77" t="n"/>
+      <c r="AU11" s="77" t="n"/>
+      <c r="AV11" s="77" t="n"/>
+      <c r="AW11" s="77" t="n"/>
+      <c r="AX11" s="77" t="n"/>
+      <c r="AY11" s="77" t="n"/>
+      <c r="AZ11" s="77" t="n"/>
+      <c r="BA11" s="78" t="n"/>
+      <c r="BB11" s="68" t="n"/>
+      <c r="BC11" s="68" t="n"/>
+      <c r="BD11" s="68" t="n"/>
+      <c r="BE11" s="68" t="n"/>
+      <c r="BF11" s="71" t="n"/>
+      <c r="BG11" s="47" t="n"/>
+      <c r="BH11" s="47" t="n"/>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="55" t="n"/>
+      <c r="B12" s="57" t="n"/>
+      <c r="C12" s="57" t="n"/>
+      <c r="D12" s="57" t="n"/>
+      <c r="E12" s="57" t="n"/>
+      <c r="F12" s="57" t="n"/>
+      <c r="G12" s="57" t="n"/>
+      <c r="H12" s="57" t="n"/>
+      <c r="I12" s="57" t="n"/>
+      <c r="J12" s="57" t="n"/>
+      <c r="K12" s="57" t="n"/>
+      <c r="L12" s="58" t="n"/>
+      <c r="M12" s="47" t="n"/>
+      <c r="N12" s="67" t="n"/>
+      <c r="O12" s="68" t="n"/>
+      <c r="P12" s="68" t="n"/>
+      <c r="Q12" s="68" t="n"/>
+      <c r="R12" s="68" t="n"/>
+      <c r="S12" s="68" t="n"/>
+      <c r="T12" s="68" t="n"/>
+      <c r="U12" s="68" t="n"/>
+      <c r="V12" s="68" t="n"/>
+      <c r="W12" s="68" t="n"/>
+      <c r="X12" s="68" t="n"/>
+      <c r="Y12" s="68" t="n"/>
+      <c r="Z12" s="68" t="n"/>
+      <c r="AA12" s="68" t="n"/>
+      <c r="AB12" s="68" t="n"/>
+      <c r="AC12" s="68" t="n"/>
+      <c r="AD12" s="68" t="n"/>
+      <c r="AE12" s="68" t="n"/>
+      <c r="AF12" s="68" t="n"/>
+      <c r="AG12" s="68" t="n"/>
+      <c r="AH12" s="68" t="n"/>
+      <c r="AI12" s="68" t="n"/>
+      <c r="AJ12" s="68" t="n"/>
+      <c r="AK12" s="68" t="n"/>
+      <c r="AL12" s="68" t="n"/>
+      <c r="AM12" s="68" t="n"/>
+      <c r="AN12" s="68" t="n"/>
+      <c r="AO12" s="68" t="n"/>
+      <c r="AP12" s="68" t="n"/>
+      <c r="AQ12" s="68" t="n"/>
+      <c r="AR12" s="68" t="n"/>
+      <c r="AS12" s="68" t="n"/>
+      <c r="AT12" s="68" t="n"/>
+      <c r="AU12" s="68" t="n"/>
+      <c r="AV12" s="68" t="n"/>
+      <c r="AW12" s="68" t="n"/>
+      <c r="AX12" s="68" t="n"/>
+      <c r="AY12" s="68" t="n"/>
+      <c r="AZ12" s="68" t="n"/>
+      <c r="BA12" s="68" t="n"/>
+      <c r="BB12" s="68" t="n"/>
+      <c r="BC12" s="68" t="n"/>
+      <c r="BD12" s="68" t="n"/>
+      <c r="BE12" s="68" t="n"/>
+      <c r="BF12" s="71" t="n"/>
+      <c r="BG12" s="47" t="n"/>
+      <c r="BH12" s="47" t="n"/>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="55" t="n"/>
+      <c r="B13" s="63" t="inlineStr">
+        <is>
+          <t>通知</t>
+        </is>
+      </c>
+      <c r="C13" s="57" t="n"/>
+      <c r="D13" s="57" t="n"/>
+      <c r="E13" s="57" t="n"/>
+      <c r="F13" s="57" t="n"/>
+      <c r="G13" s="57" t="n"/>
+      <c r="H13" s="57" t="n"/>
+      <c r="I13" s="57" t="n"/>
+      <c r="J13" s="80" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="57" t="n"/>
+      <c r="L13" s="58" t="n"/>
+      <c r="M13" s="47" t="n"/>
+      <c r="N13" s="72" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="O13" s="73" t="inlineStr">
+        <is>
+          <t>有給・無給</t>
+        </is>
+      </c>
+      <c r="P13" s="74" t="n"/>
+      <c r="Q13" s="74" t="n"/>
+      <c r="R13" s="74" t="n"/>
+      <c r="S13" s="74" t="n"/>
+      <c r="T13" s="74" t="n"/>
+      <c r="U13" s="74" t="n"/>
+      <c r="V13" s="75" t="n"/>
+      <c r="W13" s="76" t="inlineStr">
         <is>
           <t>有給</t>
         </is>
       </c>
-      <c r="AE8" s="27" t="n"/>
-      <c r="AF8" s="27" t="n"/>
-      <c r="AG8" s="27" t="n"/>
-      <c r="AH8" s="27" t="n"/>
-      <c r="AI8" s="27" t="n"/>
-      <c r="AJ8" s="27" t="n"/>
-      <c r="AK8" s="28" t="n"/>
-      <c r="AL8" s="26" t="inlineStr">
+      <c r="X13" s="77" t="n"/>
+      <c r="Y13" s="77" t="n"/>
+      <c r="Z13" s="77" t="n"/>
+      <c r="AA13" s="77" t="n"/>
+      <c r="AB13" s="77" t="n"/>
+      <c r="AC13" s="77" t="n"/>
+      <c r="AD13" s="77" t="n"/>
+      <c r="AE13" s="77" t="n"/>
+      <c r="AF13" s="78" t="n"/>
+      <c r="AG13" s="68" t="n"/>
+      <c r="AH13" s="68" t="n"/>
+      <c r="AI13" s="79" t="inlineStr">
+        <is>
+          <t>⑥</t>
+        </is>
+      </c>
+      <c r="AJ13" s="73" t="inlineStr">
         <is>
           <t>日数ルール</t>
         </is>
       </c>
-      <c r="AM8" s="27" t="n"/>
-      <c r="AN8" s="27" t="n"/>
-      <c r="AO8" s="27" t="n"/>
-      <c r="AP8" s="27" t="n"/>
-      <c r="AQ8" s="27" t="n"/>
-      <c r="AR8" s="27" t="n"/>
-      <c r="AS8" s="28" t="n"/>
-      <c r="AT8" s="26" t="inlineStr">
+      <c r="AK13" s="74" t="n"/>
+      <c r="AL13" s="74" t="n"/>
+      <c r="AM13" s="74" t="n"/>
+      <c r="AN13" s="74" t="n"/>
+      <c r="AO13" s="74" t="n"/>
+      <c r="AP13" s="74" t="n"/>
+      <c r="AQ13" s="75" t="n"/>
+      <c r="AR13" s="76" t="inlineStr">
+        <is>
+          <t>上限あり</t>
+        </is>
+      </c>
+      <c r="AS13" s="77" t="n"/>
+      <c r="AT13" s="77" t="n"/>
+      <c r="AU13" s="77" t="n"/>
+      <c r="AV13" s="77" t="n"/>
+      <c r="AW13" s="77" t="n"/>
+      <c r="AX13" s="77" t="n"/>
+      <c r="AY13" s="77" t="n"/>
+      <c r="AZ13" s="77" t="n"/>
+      <c r="BA13" s="78" t="n"/>
+      <c r="BB13" s="68" t="n"/>
+      <c r="BC13" s="68" t="n"/>
+      <c r="BD13" s="68" t="n"/>
+      <c r="BE13" s="68" t="n"/>
+      <c r="BF13" s="71" t="n"/>
+      <c r="BG13" s="47" t="n"/>
+      <c r="BH13" s="47" t="n"/>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="55" t="n"/>
+      <c r="B14" s="57" t="n"/>
+      <c r="C14" s="57" t="n"/>
+      <c r="D14" s="57" t="n"/>
+      <c r="E14" s="57" t="n"/>
+      <c r="F14" s="57" t="n"/>
+      <c r="G14" s="57" t="n"/>
+      <c r="H14" s="57" t="n"/>
+      <c r="I14" s="57" t="n"/>
+      <c r="J14" s="57" t="n"/>
+      <c r="K14" s="57" t="n"/>
+      <c r="L14" s="58" t="n"/>
+      <c r="M14" s="47" t="n"/>
+      <c r="N14" s="67" t="n"/>
+      <c r="O14" s="68" t="n"/>
+      <c r="P14" s="68" t="n"/>
+      <c r="Q14" s="68" t="n"/>
+      <c r="R14" s="68" t="n"/>
+      <c r="S14" s="68" t="n"/>
+      <c r="T14" s="68" t="n"/>
+      <c r="U14" s="68" t="n"/>
+      <c r="V14" s="68" t="n"/>
+      <c r="W14" s="68" t="n"/>
+      <c r="X14" s="68" t="n"/>
+      <c r="Y14" s="68" t="n"/>
+      <c r="Z14" s="68" t="n"/>
+      <c r="AA14" s="68" t="n"/>
+      <c r="AB14" s="68" t="n"/>
+      <c r="AC14" s="68" t="n"/>
+      <c r="AD14" s="68" t="n"/>
+      <c r="AE14" s="68" t="n"/>
+      <c r="AF14" s="68" t="n"/>
+      <c r="AG14" s="68" t="n"/>
+      <c r="AH14" s="68" t="n"/>
+      <c r="AI14" s="68" t="n"/>
+      <c r="AJ14" s="68" t="n"/>
+      <c r="AK14" s="68" t="n"/>
+      <c r="AL14" s="68" t="n"/>
+      <c r="AM14" s="68" t="n"/>
+      <c r="AN14" s="68" t="n"/>
+      <c r="AO14" s="68" t="n"/>
+      <c r="AP14" s="68" t="n"/>
+      <c r="AQ14" s="68" t="n"/>
+      <c r="AR14" s="68" t="n"/>
+      <c r="AS14" s="68" t="n"/>
+      <c r="AT14" s="68" t="n"/>
+      <c r="AU14" s="68" t="n"/>
+      <c r="AV14" s="68" t="n"/>
+      <c r="AW14" s="68" t="n"/>
+      <c r="AX14" s="68" t="n"/>
+      <c r="AY14" s="68" t="n"/>
+      <c r="AZ14" s="68" t="n"/>
+      <c r="BA14" s="68" t="n"/>
+      <c r="BB14" s="68" t="n"/>
+      <c r="BC14" s="68" t="n"/>
+      <c r="BD14" s="68" t="n"/>
+      <c r="BE14" s="68" t="n"/>
+      <c r="BF14" s="71" t="n"/>
+      <c r="BG14" s="47" t="n"/>
+      <c r="BH14" s="47" t="n"/>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="55" t="n"/>
+      <c r="B15" s="81" t="n"/>
+      <c r="C15" s="81" t="n"/>
+      <c r="D15" s="81" t="n"/>
+      <c r="E15" s="81" t="n"/>
+      <c r="F15" s="81" t="n"/>
+      <c r="G15" s="81" t="n"/>
+      <c r="H15" s="81" t="n"/>
+      <c r="I15" s="81" t="n"/>
+      <c r="J15" s="81" t="n"/>
+      <c r="K15" s="81" t="n"/>
+      <c r="L15" s="58" t="n"/>
+      <c r="M15" s="47" t="n"/>
+      <c r="N15" s="72" t="inlineStr">
+        <is>
+          <t>⑦</t>
+        </is>
+      </c>
+      <c r="O15" s="73" t="inlineStr">
+        <is>
+          <t>半日取得</t>
+        </is>
+      </c>
+      <c r="P15" s="74" t="n"/>
+      <c r="Q15" s="74" t="n"/>
+      <c r="R15" s="74" t="n"/>
+      <c r="S15" s="74" t="n"/>
+      <c r="T15" s="74" t="n"/>
+      <c r="U15" s="74" t="n"/>
+      <c r="V15" s="75" t="n"/>
+      <c r="W15" s="76" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="X15" s="77" t="n"/>
+      <c r="Y15" s="77" t="n"/>
+      <c r="Z15" s="77" t="n"/>
+      <c r="AA15" s="77" t="n"/>
+      <c r="AB15" s="77" t="n"/>
+      <c r="AC15" s="77" t="n"/>
+      <c r="AD15" s="77" t="n"/>
+      <c r="AE15" s="77" t="n"/>
+      <c r="AF15" s="78" t="n"/>
+      <c r="AG15" s="68" t="n"/>
+      <c r="AH15" s="68" t="n"/>
+      <c r="AI15" s="79" t="inlineStr">
+        <is>
+          <t>⑧</t>
+        </is>
+      </c>
+      <c r="AJ15" s="73" t="inlineStr">
+        <is>
+          <t>有効・無効</t>
+        </is>
+      </c>
+      <c r="AK15" s="74" t="n"/>
+      <c r="AL15" s="74" t="n"/>
+      <c r="AM15" s="74" t="n"/>
+      <c r="AN15" s="74" t="n"/>
+      <c r="AO15" s="74" t="n"/>
+      <c r="AP15" s="74" t="n"/>
+      <c r="AQ15" s="75" t="n"/>
+      <c r="AR15" s="76" t="inlineStr">
         <is>
           <t>有効</t>
         </is>
       </c>
-      <c r="AU8" s="27" t="n"/>
-      <c r="AV8" s="27" t="n"/>
-      <c r="AW8" s="27" t="n"/>
-      <c r="AX8" s="27" t="n"/>
-      <c r="AY8" s="27" t="n"/>
-      <c r="AZ8" s="27" t="n"/>
-      <c r="BA8" s="27" t="n"/>
-      <c r="BB8" s="27" t="n"/>
-      <c r="BC8" s="27" t="n"/>
-      <c r="BD8" s="28" t="n"/>
-    </row>
-    <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="22" t="n"/>
-      <c r="L9" s="24" t="n"/>
-      <c r="N9" s="29" t="inlineStr">
+      <c r="AS15" s="77" t="n"/>
+      <c r="AT15" s="77" t="n"/>
+      <c r="AU15" s="77" t="n"/>
+      <c r="AV15" s="77" t="n"/>
+      <c r="AW15" s="77" t="n"/>
+      <c r="AX15" s="77" t="n"/>
+      <c r="AY15" s="77" t="n"/>
+      <c r="AZ15" s="77" t="n"/>
+      <c r="BA15" s="78" t="n"/>
+      <c r="BB15" s="68" t="n"/>
+      <c r="BC15" s="68" t="n"/>
+      <c r="BD15" s="68" t="n"/>
+      <c r="BE15" s="68" t="n"/>
+      <c r="BF15" s="71" t="n"/>
+      <c r="BG15" s="47" t="n"/>
+      <c r="BH15" s="47" t="n"/>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="55" t="n"/>
+      <c r="B16" s="56" t="inlineStr">
+        <is>
+          <t>承認</t>
+        </is>
+      </c>
+      <c r="C16" s="57" t="n"/>
+      <c r="D16" s="57" t="n"/>
+      <c r="E16" s="57" t="n"/>
+      <c r="F16" s="57" t="n"/>
+      <c r="G16" s="57" t="n"/>
+      <c r="H16" s="57" t="n"/>
+      <c r="I16" s="57" t="n"/>
+      <c r="J16" s="57" t="n"/>
+      <c r="K16" s="57" t="n"/>
+      <c r="L16" s="58" t="n"/>
+      <c r="M16" s="47" t="n"/>
+      <c r="N16" s="67" t="n"/>
+      <c r="O16" s="68" t="n"/>
+      <c r="P16" s="68" t="n"/>
+      <c r="Q16" s="68" t="n"/>
+      <c r="R16" s="68" t="n"/>
+      <c r="S16" s="68" t="n"/>
+      <c r="T16" s="68" t="n"/>
+      <c r="U16" s="68" t="n"/>
+      <c r="V16" s="68" t="n"/>
+      <c r="W16" s="68" t="n"/>
+      <c r="X16" s="68" t="n"/>
+      <c r="Y16" s="68" t="n"/>
+      <c r="Z16" s="68" t="n"/>
+      <c r="AA16" s="68" t="n"/>
+      <c r="AB16" s="68" t="n"/>
+      <c r="AC16" s="68" t="n"/>
+      <c r="AD16" s="68" t="n"/>
+      <c r="AE16" s="68" t="n"/>
+      <c r="AF16" s="68" t="n"/>
+      <c r="AG16" s="68" t="n"/>
+      <c r="AH16" s="68" t="n"/>
+      <c r="AI16" s="68" t="n"/>
+      <c r="AJ16" s="68" t="n"/>
+      <c r="AK16" s="68" t="n"/>
+      <c r="AL16" s="68" t="n"/>
+      <c r="AM16" s="68" t="n"/>
+      <c r="AN16" s="68" t="n"/>
+      <c r="AO16" s="68" t="n"/>
+      <c r="AP16" s="68" t="n"/>
+      <c r="AQ16" s="68" t="n"/>
+      <c r="AR16" s="68" t="n"/>
+      <c r="AS16" s="68" t="n"/>
+      <c r="AT16" s="68" t="n"/>
+      <c r="AU16" s="68" t="n"/>
+      <c r="AV16" s="68" t="n"/>
+      <c r="AW16" s="68" t="n"/>
+      <c r="AX16" s="68" t="n"/>
+      <c r="AY16" s="68" t="n"/>
+      <c r="AZ16" s="68" t="n"/>
+      <c r="BA16" s="68" t="n"/>
+      <c r="BB16" s="68" t="n"/>
+      <c r="BC16" s="68" t="n"/>
+      <c r="BD16" s="68" t="n"/>
+      <c r="BE16" s="68" t="n"/>
+      <c r="BF16" s="71" t="n"/>
+      <c r="BG16" s="47" t="n"/>
+      <c r="BH16" s="47" t="n"/>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="55" t="n"/>
+      <c r="B17" s="63" t="inlineStr">
+        <is>
+          <t>承認待ち</t>
+        </is>
+      </c>
+      <c r="C17" s="57" t="n"/>
+      <c r="D17" s="57" t="n"/>
+      <c r="E17" s="57" t="n"/>
+      <c r="F17" s="57" t="n"/>
+      <c r="G17" s="57" t="n"/>
+      <c r="H17" s="57" t="n"/>
+      <c r="I17" s="57" t="n"/>
+      <c r="J17" s="57" t="n"/>
+      <c r="K17" s="57" t="n"/>
+      <c r="L17" s="58" t="n"/>
+      <c r="M17" s="47" t="n"/>
+      <c r="N17" s="67" t="n"/>
+      <c r="O17" s="68" t="n"/>
+      <c r="P17" s="82" t="inlineStr">
+        <is>
+          <t>名称は必須入力です。</t>
+        </is>
+      </c>
+      <c r="Q17" s="83" t="n"/>
+      <c r="R17" s="83" t="n"/>
+      <c r="S17" s="83" t="n"/>
+      <c r="T17" s="83" t="n"/>
+      <c r="U17" s="83" t="n"/>
+      <c r="V17" s="83" t="n"/>
+      <c r="W17" s="83" t="n"/>
+      <c r="X17" s="83" t="n"/>
+      <c r="Y17" s="83" t="n"/>
+      <c r="Z17" s="83" t="n"/>
+      <c r="AA17" s="83" t="n"/>
+      <c r="AB17" s="83" t="n"/>
+      <c r="AC17" s="83" t="n"/>
+      <c r="AD17" s="83" t="n"/>
+      <c r="AE17" s="83" t="n"/>
+      <c r="AF17" s="83" t="n"/>
+      <c r="AG17" s="83" t="n"/>
+      <c r="AH17" s="83" t="n"/>
+      <c r="AI17" s="83" t="n"/>
+      <c r="AJ17" s="83" t="n"/>
+      <c r="AK17" s="83" t="n"/>
+      <c r="AL17" s="83" t="n"/>
+      <c r="AM17" s="83" t="n"/>
+      <c r="AN17" s="83" t="n"/>
+      <c r="AO17" s="83" t="n"/>
+      <c r="AP17" s="83" t="n"/>
+      <c r="AQ17" s="83" t="n"/>
+      <c r="AR17" s="83" t="n"/>
+      <c r="AS17" s="83" t="n"/>
+      <c r="AT17" s="83" t="n"/>
+      <c r="AU17" s="83" t="n"/>
+      <c r="AV17" s="83" t="n"/>
+      <c r="AW17" s="83" t="n"/>
+      <c r="AX17" s="83" t="n"/>
+      <c r="AY17" s="83" t="n"/>
+      <c r="AZ17" s="83" t="n"/>
+      <c r="BA17" s="83" t="n"/>
+      <c r="BB17" s="83" t="n"/>
+      <c r="BC17" s="83" t="n"/>
+      <c r="BD17" s="83" t="n"/>
+      <c r="BE17" s="68" t="n"/>
+      <c r="BF17" s="71" t="n"/>
+      <c r="BG17" s="47" t="n"/>
+      <c r="BH17" s="47" t="n"/>
+    </row>
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" s="55" t="n"/>
+      <c r="B18" s="57" t="n"/>
+      <c r="C18" s="57" t="n"/>
+      <c r="D18" s="57" t="n"/>
+      <c r="E18" s="57" t="n"/>
+      <c r="F18" s="57" t="n"/>
+      <c r="G18" s="57" t="n"/>
+      <c r="H18" s="57" t="n"/>
+      <c r="I18" s="57" t="n"/>
+      <c r="J18" s="57" t="n"/>
+      <c r="K18" s="57" t="n"/>
+      <c r="L18" s="58" t="n"/>
+      <c r="M18" s="47" t="n"/>
+      <c r="N18" s="67" t="n"/>
+      <c r="O18" s="68" t="n"/>
+      <c r="P18" s="68" t="n"/>
+      <c r="Q18" s="68" t="n"/>
+      <c r="R18" s="68" t="n"/>
+      <c r="S18" s="68" t="n"/>
+      <c r="T18" s="68" t="n"/>
+      <c r="U18" s="68" t="n"/>
+      <c r="V18" s="68" t="n"/>
+      <c r="W18" s="68" t="n"/>
+      <c r="X18" s="68" t="n"/>
+      <c r="Y18" s="68" t="n"/>
+      <c r="Z18" s="68" t="n"/>
+      <c r="AA18" s="68" t="n"/>
+      <c r="AB18" s="68" t="n"/>
+      <c r="AC18" s="68" t="n"/>
+      <c r="AD18" s="68" t="n"/>
+      <c r="AE18" s="68" t="n"/>
+      <c r="AF18" s="68" t="n"/>
+      <c r="AG18" s="68" t="n"/>
+      <c r="AH18" s="68" t="n"/>
+      <c r="AI18" s="68" t="n"/>
+      <c r="AJ18" s="68" t="n"/>
+      <c r="AK18" s="68" t="n"/>
+      <c r="AL18" s="68" t="n"/>
+      <c r="AM18" s="68" t="n"/>
+      <c r="AN18" s="68" t="n"/>
+      <c r="AO18" s="68" t="n"/>
+      <c r="AP18" s="68" t="n"/>
+      <c r="AQ18" s="68" t="n"/>
+      <c r="AR18" s="68" t="n"/>
+      <c r="AS18" s="68" t="n"/>
+      <c r="AT18" s="68" t="n"/>
+      <c r="AU18" s="68" t="n"/>
+      <c r="AV18" s="68" t="n"/>
+      <c r="AW18" s="68" t="n"/>
+      <c r="AX18" s="68" t="n"/>
+      <c r="AY18" s="68" t="n"/>
+      <c r="AZ18" s="68" t="n"/>
+      <c r="BA18" s="68" t="n"/>
+      <c r="BB18" s="68" t="n"/>
+      <c r="BC18" s="68" t="n"/>
+      <c r="BD18" s="68" t="n"/>
+      <c r="BE18" s="68" t="n"/>
+      <c r="BF18" s="71" t="n"/>
+      <c r="BG18" s="47" t="n"/>
+      <c r="BH18" s="47" t="n"/>
+    </row>
+    <row r="19" ht="17" customHeight="1">
+      <c r="A19" s="55" t="n"/>
+      <c r="B19" s="81" t="n"/>
+      <c r="C19" s="81" t="n"/>
+      <c r="D19" s="81" t="n"/>
+      <c r="E19" s="81" t="n"/>
+      <c r="F19" s="81" t="n"/>
+      <c r="G19" s="81" t="n"/>
+      <c r="H19" s="81" t="n"/>
+      <c r="I19" s="81" t="n"/>
+      <c r="J19" s="81" t="n"/>
+      <c r="K19" s="81" t="n"/>
+      <c r="L19" s="58" t="n"/>
+      <c r="M19" s="47" t="n"/>
+      <c r="N19" s="67" t="n"/>
+      <c r="O19" s="68" t="n"/>
+      <c r="P19" s="52" t="inlineStr">
+        <is>
+          <t>登録する</t>
+        </is>
+      </c>
+      <c r="Q19" s="53" t="n"/>
+      <c r="R19" s="53" t="n"/>
+      <c r="S19" s="53" t="n"/>
+      <c r="T19" s="53" t="n"/>
+      <c r="U19" s="53" t="n"/>
+      <c r="V19" s="53" t="n"/>
+      <c r="W19" s="53" t="n"/>
+      <c r="X19" s="53" t="n"/>
+      <c r="Y19" s="53" t="n"/>
+      <c r="Z19" s="54" t="n"/>
+      <c r="AA19" s="68" t="n"/>
+      <c r="AB19" s="84" t="inlineStr">
+        <is>
+          <t>キャンセル</t>
+        </is>
+      </c>
+      <c r="AC19" s="85" t="n"/>
+      <c r="AD19" s="85" t="n"/>
+      <c r="AE19" s="85" t="n"/>
+      <c r="AF19" s="85" t="n"/>
+      <c r="AG19" s="85" t="n"/>
+      <c r="AH19" s="85" t="n"/>
+      <c r="AI19" s="85" t="n"/>
+      <c r="AJ19" s="85" t="n"/>
+      <c r="AK19" s="85" t="n"/>
+      <c r="AL19" s="86" t="n"/>
+      <c r="AM19" s="68" t="n"/>
+      <c r="AN19" s="68" t="n"/>
+      <c r="AO19" s="68" t="n"/>
+      <c r="AP19" s="68" t="n"/>
+      <c r="AQ19" s="68" t="n"/>
+      <c r="AR19" s="68" t="n"/>
+      <c r="AS19" s="68" t="n"/>
+      <c r="AT19" s="68" t="n"/>
+      <c r="AU19" s="68" t="n"/>
+      <c r="AV19" s="68" t="n"/>
+      <c r="AW19" s="68" t="n"/>
+      <c r="AX19" s="68" t="n"/>
+      <c r="AY19" s="68" t="n"/>
+      <c r="AZ19" s="68" t="n"/>
+      <c r="BA19" s="68" t="n"/>
+      <c r="BB19" s="68" t="n"/>
+      <c r="BC19" s="68" t="n"/>
+      <c r="BD19" s="68" t="n"/>
+      <c r="BE19" s="68" t="n"/>
+      <c r="BF19" s="71" t="n"/>
+      <c r="BG19" s="47" t="n"/>
+      <c r="BH19" s="47" t="n"/>
+    </row>
+    <row r="20" ht="17" customHeight="1">
+      <c r="A20" s="55" t="n"/>
+      <c r="B20" s="56" t="inlineStr">
+        <is>
+          <t>管理</t>
+        </is>
+      </c>
+      <c r="C20" s="57" t="n"/>
+      <c r="D20" s="57" t="n"/>
+      <c r="E20" s="57" t="n"/>
+      <c r="F20" s="57" t="n"/>
+      <c r="G20" s="57" t="n"/>
+      <c r="H20" s="57" t="n"/>
+      <c r="I20" s="57" t="n"/>
+      <c r="J20" s="57" t="n"/>
+      <c r="K20" s="57" t="n"/>
+      <c r="L20" s="58" t="n"/>
+      <c r="M20" s="47" t="n"/>
+      <c r="N20" s="67" t="n"/>
+      <c r="O20" s="79" t="inlineStr">
+        <is>
+          <t>⑨</t>
+        </is>
+      </c>
+      <c r="P20" s="60" t="n"/>
+      <c r="Q20" s="61" t="n"/>
+      <c r="R20" s="61" t="n"/>
+      <c r="S20" s="61" t="n"/>
+      <c r="T20" s="61" t="n"/>
+      <c r="U20" s="61" t="n"/>
+      <c r="V20" s="61" t="n"/>
+      <c r="W20" s="61" t="n"/>
+      <c r="X20" s="61" t="n"/>
+      <c r="Y20" s="61" t="n"/>
+      <c r="Z20" s="62" t="n"/>
+      <c r="AA20" s="68" t="n"/>
+      <c r="AB20" s="87" t="n"/>
+      <c r="AC20" s="88" t="n"/>
+      <c r="AD20" s="88" t="n"/>
+      <c r="AE20" s="88" t="n"/>
+      <c r="AF20" s="88" t="n"/>
+      <c r="AG20" s="88" t="n"/>
+      <c r="AH20" s="88" t="n"/>
+      <c r="AI20" s="88" t="n"/>
+      <c r="AJ20" s="88" t="n"/>
+      <c r="AK20" s="88" t="n"/>
+      <c r="AL20" s="89" t="n"/>
+      <c r="AM20" s="68" t="n"/>
+      <c r="AN20" s="68" t="n"/>
+      <c r="AO20" s="68" t="n"/>
+      <c r="AP20" s="68" t="n"/>
+      <c r="AQ20" s="68" t="n"/>
+      <c r="AR20" s="68" t="n"/>
+      <c r="AS20" s="68" t="n"/>
+      <c r="AT20" s="68" t="n"/>
+      <c r="AU20" s="68" t="n"/>
+      <c r="AV20" s="68" t="n"/>
+      <c r="AW20" s="68" t="n"/>
+      <c r="AX20" s="68" t="n"/>
+      <c r="AY20" s="68" t="n"/>
+      <c r="AZ20" s="68" t="n"/>
+      <c r="BA20" s="68" t="n"/>
+      <c r="BB20" s="68" t="n"/>
+      <c r="BC20" s="68" t="n"/>
+      <c r="BD20" s="68" t="n"/>
+      <c r="BE20" s="68" t="n"/>
+      <c r="BF20" s="71" t="n"/>
+      <c r="BG20" s="47" t="n"/>
+      <c r="BH20" s="47" t="n"/>
+    </row>
+    <row r="21" ht="17" customHeight="1">
+      <c r="A21" s="55" t="n"/>
+      <c r="B21" s="63" t="inlineStr">
+        <is>
+          <t>月次集計</t>
+        </is>
+      </c>
+      <c r="C21" s="57" t="n"/>
+      <c r="D21" s="57" t="n"/>
+      <c r="E21" s="57" t="n"/>
+      <c r="F21" s="57" t="n"/>
+      <c r="G21" s="57" t="n"/>
+      <c r="H21" s="57" t="n"/>
+      <c r="I21" s="57" t="n"/>
+      <c r="J21" s="57" t="n"/>
+      <c r="K21" s="57" t="n"/>
+      <c r="L21" s="58" t="n"/>
+      <c r="M21" s="47" t="n"/>
+      <c r="N21" s="67" t="n"/>
+      <c r="O21" s="68" t="n"/>
+      <c r="P21" s="68" t="n"/>
+      <c r="Q21" s="68" t="n"/>
+      <c r="R21" s="68" t="n"/>
+      <c r="S21" s="68" t="n"/>
+      <c r="T21" s="68" t="n"/>
+      <c r="U21" s="68" t="n"/>
+      <c r="V21" s="68" t="n"/>
+      <c r="W21" s="68" t="n"/>
+      <c r="X21" s="68" t="n"/>
+      <c r="Y21" s="68" t="n"/>
+      <c r="Z21" s="68" t="n"/>
+      <c r="AA21" s="68" t="n"/>
+      <c r="AB21" s="68" t="n"/>
+      <c r="AC21" s="68" t="n"/>
+      <c r="AD21" s="68" t="n"/>
+      <c r="AE21" s="68" t="n"/>
+      <c r="AF21" s="68" t="n"/>
+      <c r="AG21" s="68" t="n"/>
+      <c r="AH21" s="68" t="n"/>
+      <c r="AI21" s="68" t="n"/>
+      <c r="AJ21" s="68" t="n"/>
+      <c r="AK21" s="68" t="n"/>
+      <c r="AL21" s="68" t="n"/>
+      <c r="AM21" s="68" t="n"/>
+      <c r="AN21" s="68" t="n"/>
+      <c r="AO21" s="68" t="n"/>
+      <c r="AP21" s="68" t="n"/>
+      <c r="AQ21" s="68" t="n"/>
+      <c r="AR21" s="68" t="n"/>
+      <c r="AS21" s="68" t="n"/>
+      <c r="AT21" s="68" t="n"/>
+      <c r="AU21" s="68" t="n"/>
+      <c r="AV21" s="68" t="n"/>
+      <c r="AW21" s="68" t="n"/>
+      <c r="AX21" s="68" t="n"/>
+      <c r="AY21" s="68" t="n"/>
+      <c r="AZ21" s="68" t="n"/>
+      <c r="BA21" s="68" t="n"/>
+      <c r="BB21" s="68" t="n"/>
+      <c r="BC21" s="68" t="n"/>
+      <c r="BD21" s="68" t="n"/>
+      <c r="BE21" s="68" t="n"/>
+      <c r="BF21" s="71" t="n"/>
+      <c r="BG21" s="47" t="n"/>
+      <c r="BH21" s="47" t="n"/>
+    </row>
+    <row r="22" ht="17" customHeight="1">
+      <c r="A22" s="55" t="n"/>
+      <c r="B22" s="57" t="n"/>
+      <c r="C22" s="57" t="n"/>
+      <c r="D22" s="57" t="n"/>
+      <c r="E22" s="57" t="n"/>
+      <c r="F22" s="57" t="n"/>
+      <c r="G22" s="57" t="n"/>
+      <c r="H22" s="57" t="n"/>
+      <c r="I22" s="57" t="n"/>
+      <c r="J22" s="57" t="n"/>
+      <c r="K22" s="57" t="n"/>
+      <c r="L22" s="58" t="n"/>
+      <c r="M22" s="47" t="n"/>
+      <c r="N22" s="67" t="n"/>
+      <c r="O22" s="68" t="n"/>
+      <c r="P22" s="68" t="n"/>
+      <c r="Q22" s="68" t="n"/>
+      <c r="R22" s="68" t="n"/>
+      <c r="S22" s="68" t="n"/>
+      <c r="T22" s="68" t="n"/>
+      <c r="U22" s="68" t="n"/>
+      <c r="V22" s="68" t="n"/>
+      <c r="W22" s="68" t="n"/>
+      <c r="X22" s="68" t="n"/>
+      <c r="Y22" s="68" t="n"/>
+      <c r="Z22" s="68" t="n"/>
+      <c r="AA22" s="68" t="n"/>
+      <c r="AB22" s="68" t="n"/>
+      <c r="AC22" s="68" t="n"/>
+      <c r="AD22" s="68" t="n"/>
+      <c r="AE22" s="68" t="n"/>
+      <c r="AF22" s="68" t="n"/>
+      <c r="AG22" s="68" t="n"/>
+      <c r="AH22" s="68" t="n"/>
+      <c r="AI22" s="68" t="n"/>
+      <c r="AJ22" s="68" t="n"/>
+      <c r="AK22" s="68" t="n"/>
+      <c r="AL22" s="68" t="n"/>
+      <c r="AM22" s="68" t="n"/>
+      <c r="AN22" s="68" t="n"/>
+      <c r="AO22" s="68" t="n"/>
+      <c r="AP22" s="68" t="n"/>
+      <c r="AQ22" s="68" t="n"/>
+      <c r="AR22" s="68" t="n"/>
+      <c r="AS22" s="68" t="n"/>
+      <c r="AT22" s="68" t="n"/>
+      <c r="AU22" s="68" t="n"/>
+      <c r="AV22" s="68" t="n"/>
+      <c r="AW22" s="68" t="n"/>
+      <c r="AX22" s="68" t="n"/>
+      <c r="AY22" s="68" t="n"/>
+      <c r="AZ22" s="68" t="n"/>
+      <c r="BA22" s="68" t="n"/>
+      <c r="BB22" s="68" t="n"/>
+      <c r="BC22" s="68" t="n"/>
+      <c r="BD22" s="68" t="n"/>
+      <c r="BE22" s="68" t="n"/>
+      <c r="BF22" s="71" t="n"/>
+      <c r="BG22" s="47" t="n"/>
+      <c r="BH22" s="47" t="n"/>
+    </row>
+    <row r="23" ht="17" customHeight="1">
+      <c r="A23" s="55" t="n"/>
+      <c r="B23" s="63" t="inlineStr">
+        <is>
+          <t>ユーザー管理</t>
+        </is>
+      </c>
+      <c r="C23" s="57" t="n"/>
+      <c r="D23" s="57" t="n"/>
+      <c r="E23" s="57" t="n"/>
+      <c r="F23" s="57" t="n"/>
+      <c r="G23" s="57" t="n"/>
+      <c r="H23" s="57" t="n"/>
+      <c r="I23" s="57" t="n"/>
+      <c r="J23" s="57" t="n"/>
+      <c r="K23" s="57" t="n"/>
+      <c r="L23" s="58" t="n"/>
+      <c r="M23" s="47" t="n"/>
+      <c r="N23" s="67" t="n"/>
+      <c r="O23" s="68" t="n"/>
+      <c r="P23" s="68" t="n"/>
+      <c r="Q23" s="68" t="n"/>
+      <c r="R23" s="68" t="n"/>
+      <c r="S23" s="68" t="n"/>
+      <c r="T23" s="68" t="n"/>
+      <c r="U23" s="68" t="n"/>
+      <c r="V23" s="68" t="n"/>
+      <c r="W23" s="68" t="n"/>
+      <c r="X23" s="68" t="n"/>
+      <c r="Y23" s="68" t="n"/>
+      <c r="Z23" s="68" t="n"/>
+      <c r="AA23" s="68" t="n"/>
+      <c r="AB23" s="68" t="n"/>
+      <c r="AC23" s="68" t="n"/>
+      <c r="AD23" s="68" t="n"/>
+      <c r="AE23" s="68" t="n"/>
+      <c r="AF23" s="68" t="n"/>
+      <c r="AG23" s="68" t="n"/>
+      <c r="AH23" s="68" t="n"/>
+      <c r="AI23" s="68" t="n"/>
+      <c r="AJ23" s="68" t="n"/>
+      <c r="AK23" s="68" t="n"/>
+      <c r="AL23" s="68" t="n"/>
+      <c r="AM23" s="68" t="n"/>
+      <c r="AN23" s="68" t="n"/>
+      <c r="AO23" s="68" t="n"/>
+      <c r="AP23" s="68" t="n"/>
+      <c r="AQ23" s="68" t="n"/>
+      <c r="AR23" s="68" t="n"/>
+      <c r="AS23" s="68" t="n"/>
+      <c r="AT23" s="68" t="n"/>
+      <c r="AU23" s="68" t="n"/>
+      <c r="AV23" s="68" t="n"/>
+      <c r="AW23" s="68" t="n"/>
+      <c r="AX23" s="68" t="n"/>
+      <c r="AY23" s="68" t="n"/>
+      <c r="AZ23" s="68" t="n"/>
+      <c r="BA23" s="68" t="n"/>
+      <c r="BB23" s="68" t="n"/>
+      <c r="BC23" s="68" t="n"/>
+      <c r="BD23" s="68" t="n"/>
+      <c r="BE23" s="68" t="n"/>
+      <c r="BF23" s="71" t="n"/>
+      <c r="BG23" s="47" t="n"/>
+      <c r="BH23" s="47" t="n"/>
+    </row>
+    <row r="24" ht="17" customHeight="1">
+      <c r="A24" s="55" t="n"/>
+      <c r="B24" s="57" t="n"/>
+      <c r="C24" s="57" t="n"/>
+      <c r="D24" s="57" t="n"/>
+      <c r="E24" s="57" t="n"/>
+      <c r="F24" s="57" t="n"/>
+      <c r="G24" s="57" t="n"/>
+      <c r="H24" s="57" t="n"/>
+      <c r="I24" s="57" t="n"/>
+      <c r="J24" s="57" t="n"/>
+      <c r="K24" s="57" t="n"/>
+      <c r="L24" s="58" t="n"/>
+      <c r="M24" s="47" t="n"/>
+      <c r="N24" s="90" t="n"/>
+      <c r="O24" s="91" t="n"/>
+      <c r="P24" s="91" t="n"/>
+      <c r="Q24" s="91" t="n"/>
+      <c r="R24" s="91" t="n"/>
+      <c r="S24" s="91" t="n"/>
+      <c r="T24" s="91" t="n"/>
+      <c r="U24" s="91" t="n"/>
+      <c r="V24" s="91" t="n"/>
+      <c r="W24" s="91" t="n"/>
+      <c r="X24" s="91" t="n"/>
+      <c r="Y24" s="91" t="n"/>
+      <c r="Z24" s="91" t="n"/>
+      <c r="AA24" s="91" t="n"/>
+      <c r="AB24" s="91" t="n"/>
+      <c r="AC24" s="91" t="n"/>
+      <c r="AD24" s="91" t="n"/>
+      <c r="AE24" s="91" t="n"/>
+      <c r="AF24" s="91" t="n"/>
+      <c r="AG24" s="91" t="n"/>
+      <c r="AH24" s="91" t="n"/>
+      <c r="AI24" s="91" t="n"/>
+      <c r="AJ24" s="91" t="n"/>
+      <c r="AK24" s="91" t="n"/>
+      <c r="AL24" s="91" t="n"/>
+      <c r="AM24" s="91" t="n"/>
+      <c r="AN24" s="91" t="n"/>
+      <c r="AO24" s="91" t="n"/>
+      <c r="AP24" s="91" t="n"/>
+      <c r="AQ24" s="91" t="n"/>
+      <c r="AR24" s="91" t="n"/>
+      <c r="AS24" s="91" t="n"/>
+      <c r="AT24" s="91" t="n"/>
+      <c r="AU24" s="91" t="n"/>
+      <c r="AV24" s="91" t="n"/>
+      <c r="AW24" s="91" t="n"/>
+      <c r="AX24" s="91" t="n"/>
+      <c r="AY24" s="91" t="n"/>
+      <c r="AZ24" s="91" t="n"/>
+      <c r="BA24" s="91" t="n"/>
+      <c r="BB24" s="91" t="n"/>
+      <c r="BC24" s="91" t="n"/>
+      <c r="BD24" s="91" t="n"/>
+      <c r="BE24" s="91" t="n"/>
+      <c r="BF24" s="92" t="n"/>
+      <c r="BG24" s="47" t="n"/>
+      <c r="BH24" s="47" t="n"/>
+    </row>
+    <row r="25" ht="17" customHeight="1">
+      <c r="A25" s="55" t="n"/>
+      <c r="B25" s="63" t="inlineStr">
+        <is>
+          <t>休暇付与</t>
+        </is>
+      </c>
+      <c r="C25" s="57" t="n"/>
+      <c r="D25" s="57" t="n"/>
+      <c r="E25" s="57" t="n"/>
+      <c r="F25" s="57" t="n"/>
+      <c r="G25" s="57" t="n"/>
+      <c r="H25" s="57" t="n"/>
+      <c r="I25" s="57" t="n"/>
+      <c r="J25" s="57" t="n"/>
+      <c r="K25" s="57" t="n"/>
+      <c r="L25" s="58" t="n"/>
+      <c r="M25" s="47" t="n"/>
+      <c r="N25" s="47" t="n"/>
+      <c r="O25" s="47" t="n"/>
+      <c r="P25" s="47" t="n"/>
+      <c r="Q25" s="47" t="n"/>
+      <c r="R25" s="47" t="n"/>
+      <c r="S25" s="47" t="n"/>
+      <c r="T25" s="47" t="n"/>
+      <c r="U25" s="47" t="n"/>
+      <c r="V25" s="47" t="n"/>
+      <c r="W25" s="47" t="n"/>
+      <c r="X25" s="47" t="n"/>
+      <c r="Y25" s="47" t="n"/>
+      <c r="Z25" s="47" t="n"/>
+      <c r="AA25" s="47" t="n"/>
+      <c r="AB25" s="47" t="n"/>
+      <c r="AC25" s="47" t="n"/>
+      <c r="AD25" s="47" t="n"/>
+      <c r="AE25" s="47" t="n"/>
+      <c r="AF25" s="47" t="n"/>
+      <c r="AG25" s="47" t="n"/>
+      <c r="AH25" s="47" t="n"/>
+      <c r="AI25" s="47" t="n"/>
+      <c r="AJ25" s="47" t="n"/>
+      <c r="AK25" s="47" t="n"/>
+      <c r="AL25" s="47" t="n"/>
+      <c r="AM25" s="47" t="n"/>
+      <c r="AN25" s="47" t="n"/>
+      <c r="AO25" s="47" t="n"/>
+      <c r="AP25" s="47" t="n"/>
+      <c r="AQ25" s="47" t="n"/>
+      <c r="AR25" s="47" t="n"/>
+      <c r="AS25" s="47" t="n"/>
+      <c r="AT25" s="47" t="n"/>
+      <c r="AU25" s="47" t="n"/>
+      <c r="AV25" s="47" t="n"/>
+      <c r="AW25" s="47" t="n"/>
+      <c r="AX25" s="47" t="n"/>
+      <c r="AY25" s="47" t="n"/>
+      <c r="AZ25" s="47" t="n"/>
+      <c r="BA25" s="47" t="n"/>
+      <c r="BB25" s="47" t="n"/>
+      <c r="BC25" s="47" t="n"/>
+      <c r="BD25" s="47" t="n"/>
+      <c r="BE25" s="47" t="n"/>
+      <c r="BF25" s="47" t="n"/>
+      <c r="BG25" s="47" t="n"/>
+      <c r="BH25" s="47" t="n"/>
+    </row>
+    <row r="26" ht="17" customHeight="1">
+      <c r="A26" s="55" t="n"/>
+      <c r="B26" s="57" t="n"/>
+      <c r="C26" s="57" t="n"/>
+      <c r="D26" s="57" t="n"/>
+      <c r="E26" s="57" t="n"/>
+      <c r="F26" s="57" t="n"/>
+      <c r="G26" s="57" t="n"/>
+      <c r="H26" s="57" t="n"/>
+      <c r="I26" s="57" t="n"/>
+      <c r="J26" s="57" t="n"/>
+      <c r="K26" s="57" t="n"/>
+      <c r="L26" s="58" t="n"/>
+      <c r="M26" s="47" t="n"/>
+      <c r="N26" s="47" t="n"/>
+      <c r="O26" s="47" t="n"/>
+      <c r="P26" s="47" t="n"/>
+      <c r="Q26" s="47" t="n"/>
+      <c r="R26" s="47" t="n"/>
+      <c r="S26" s="47" t="n"/>
+      <c r="T26" s="47" t="n"/>
+      <c r="U26" s="47" t="n"/>
+      <c r="V26" s="47" t="n"/>
+      <c r="W26" s="47" t="n"/>
+      <c r="X26" s="47" t="n"/>
+      <c r="Y26" s="47" t="n"/>
+      <c r="Z26" s="47" t="n"/>
+      <c r="AA26" s="47" t="n"/>
+      <c r="AB26" s="47" t="n"/>
+      <c r="AC26" s="47" t="n"/>
+      <c r="AD26" s="47" t="n"/>
+      <c r="AE26" s="47" t="n"/>
+      <c r="AF26" s="47" t="n"/>
+      <c r="AG26" s="47" t="n"/>
+      <c r="AH26" s="47" t="n"/>
+      <c r="AI26" s="47" t="n"/>
+      <c r="AJ26" s="47" t="n"/>
+      <c r="AK26" s="47" t="n"/>
+      <c r="AL26" s="47" t="n"/>
+      <c r="AM26" s="47" t="n"/>
+      <c r="AN26" s="47" t="n"/>
+      <c r="AO26" s="47" t="n"/>
+      <c r="AP26" s="47" t="n"/>
+      <c r="AQ26" s="47" t="n"/>
+      <c r="AR26" s="47" t="n"/>
+      <c r="AS26" s="47" t="n"/>
+      <c r="AT26" s="47" t="n"/>
+      <c r="AU26" s="47" t="n"/>
+      <c r="AV26" s="47" t="n"/>
+      <c r="AW26" s="47" t="n"/>
+      <c r="AX26" s="47" t="n"/>
+      <c r="AY26" s="47" t="n"/>
+      <c r="AZ26" s="47" t="n"/>
+      <c r="BA26" s="47" t="n"/>
+      <c r="BB26" s="47" t="n"/>
+      <c r="BC26" s="47" t="n"/>
+      <c r="BD26" s="47" t="n"/>
+      <c r="BE26" s="47" t="n"/>
+      <c r="BF26" s="47" t="n"/>
+      <c r="BG26" s="47" t="n"/>
+      <c r="BH26" s="47" t="n"/>
+    </row>
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="55" t="n"/>
+      <c r="B27" s="93" t="inlineStr">
+        <is>
+          <t>休暇種別</t>
+        </is>
+      </c>
+      <c r="C27" s="94" t="n"/>
+      <c r="D27" s="94" t="n"/>
+      <c r="E27" s="94" t="n"/>
+      <c r="F27" s="94" t="n"/>
+      <c r="G27" s="94" t="n"/>
+      <c r="H27" s="94" t="n"/>
+      <c r="I27" s="94" t="n"/>
+      <c r="J27" s="94" t="n"/>
+      <c r="K27" s="94" t="n"/>
+      <c r="L27" s="58" t="n"/>
+      <c r="M27" s="47" t="n"/>
+      <c r="N27" s="59" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="O27" s="73" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="P27" s="74" t="n"/>
+      <c r="Q27" s="74" t="n"/>
+      <c r="R27" s="74" t="n"/>
+      <c r="S27" s="74" t="n"/>
+      <c r="T27" s="74" t="n"/>
+      <c r="U27" s="74" t="n"/>
+      <c r="V27" s="75" t="n"/>
+      <c r="W27" s="73" t="inlineStr">
+        <is>
+          <t>法的根拠</t>
+        </is>
+      </c>
+      <c r="X27" s="74" t="n"/>
+      <c r="Y27" s="74" t="n"/>
+      <c r="Z27" s="74" t="n"/>
+      <c r="AA27" s="74" t="n"/>
+      <c r="AB27" s="74" t="n"/>
+      <c r="AC27" s="74" t="n"/>
+      <c r="AD27" s="74" t="n"/>
+      <c r="AE27" s="74" t="n"/>
+      <c r="AF27" s="75" t="n"/>
+      <c r="AG27" s="95" t="inlineStr">
+        <is>
+          <t>有給</t>
+        </is>
+      </c>
+      <c r="AH27" s="74" t="n"/>
+      <c r="AI27" s="74" t="n"/>
+      <c r="AJ27" s="75" t="n"/>
+      <c r="AK27" s="95" t="inlineStr">
+        <is>
+          <t>日数ルール</t>
+        </is>
+      </c>
+      <c r="AL27" s="74" t="n"/>
+      <c r="AM27" s="74" t="n"/>
+      <c r="AN27" s="74" t="n"/>
+      <c r="AO27" s="74" t="n"/>
+      <c r="AP27" s="75" t="n"/>
+      <c r="AQ27" s="95" t="inlineStr">
+        <is>
+          <t>半日</t>
+        </is>
+      </c>
+      <c r="AR27" s="74" t="n"/>
+      <c r="AS27" s="75" t="n"/>
+      <c r="AT27" s="95" t="inlineStr">
+        <is>
+          <t>有効</t>
+        </is>
+      </c>
+      <c r="AU27" s="74" t="n"/>
+      <c r="AV27" s="74" t="n"/>
+      <c r="AW27" s="75" t="n"/>
+      <c r="AX27" s="95" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="AY27" s="74" t="n"/>
+      <c r="AZ27" s="75" t="n"/>
+      <c r="BA27" s="47" t="n"/>
+      <c r="BB27" s="47" t="n"/>
+      <c r="BC27" s="47" t="n"/>
+      <c r="BD27" s="47" t="n"/>
+      <c r="BE27" s="47" t="n"/>
+      <c r="BF27" s="47" t="n"/>
+      <c r="BG27" s="47" t="n"/>
+      <c r="BH27" s="47" t="n"/>
+    </row>
+    <row r="28" ht="17" customHeight="1">
+      <c r="A28" s="55" t="n"/>
+      <c r="B28" s="94" t="n"/>
+      <c r="C28" s="94" t="n"/>
+      <c r="D28" s="94" t="n"/>
+      <c r="E28" s="94" t="n"/>
+      <c r="F28" s="94" t="n"/>
+      <c r="G28" s="94" t="n"/>
+      <c r="H28" s="94" t="n"/>
+      <c r="I28" s="94" t="n"/>
+      <c r="J28" s="94" t="n"/>
+      <c r="K28" s="94" t="n"/>
+      <c r="L28" s="58" t="n"/>
+      <c r="M28" s="47" t="n"/>
+      <c r="N28" s="47" t="n"/>
+      <c r="O28" s="96" t="inlineStr">
         <is>
           <t>年次有給休暇</t>
         </is>
       </c>
-      <c r="O9" s="27" t="n"/>
-      <c r="P9" s="27" t="n"/>
-      <c r="Q9" s="27" t="n"/>
-      <c r="R9" s="27" t="n"/>
-      <c r="S9" s="27" t="n"/>
-      <c r="T9" s="27" t="n"/>
-      <c r="U9" s="28" t="n"/>
-      <c r="V9" s="29" t="inlineStr">
-        <is>
-          <t>労基法39条</t>
-        </is>
-      </c>
-      <c r="W9" s="27" t="n"/>
-      <c r="X9" s="27" t="n"/>
-      <c r="Y9" s="27" t="n"/>
-      <c r="Z9" s="27" t="n"/>
-      <c r="AA9" s="27" t="n"/>
-      <c r="AB9" s="27" t="n"/>
-      <c r="AC9" s="28" t="n"/>
-      <c r="AD9" s="29" t="inlineStr">
+      <c r="P28" s="77" t="n"/>
+      <c r="Q28" s="77" t="n"/>
+      <c r="R28" s="77" t="n"/>
+      <c r="S28" s="77" t="n"/>
+      <c r="T28" s="77" t="n"/>
+      <c r="U28" s="77" t="n"/>
+      <c r="V28" s="78" t="n"/>
+      <c r="W28" s="96" t="inlineStr">
+        <is>
+          <t>労働基準法第39条</t>
+        </is>
+      </c>
+      <c r="X28" s="77" t="n"/>
+      <c r="Y28" s="77" t="n"/>
+      <c r="Z28" s="77" t="n"/>
+      <c r="AA28" s="77" t="n"/>
+      <c r="AB28" s="77" t="n"/>
+      <c r="AC28" s="77" t="n"/>
+      <c r="AD28" s="77" t="n"/>
+      <c r="AE28" s="77" t="n"/>
+      <c r="AF28" s="78" t="n"/>
+      <c r="AG28" s="97" t="inlineStr">
         <is>
           <t>有給</t>
         </is>
       </c>
-      <c r="AE9" s="27" t="n"/>
-      <c r="AF9" s="27" t="n"/>
-      <c r="AG9" s="27" t="n"/>
-      <c r="AH9" s="27" t="n"/>
-      <c r="AI9" s="27" t="n"/>
-      <c r="AJ9" s="27" t="n"/>
-      <c r="AK9" s="28" t="n"/>
-      <c r="AL9" s="29" t="inlineStr">
-        <is>
-          <t>上限付き</t>
-        </is>
-      </c>
-      <c r="AM9" s="27" t="n"/>
-      <c r="AN9" s="27" t="n"/>
-      <c r="AO9" s="27" t="n"/>
-      <c r="AP9" s="27" t="n"/>
-      <c r="AQ9" s="27" t="n"/>
-      <c r="AR9" s="27" t="n"/>
-      <c r="AS9" s="28" t="n"/>
-      <c r="AT9" s="29" t="inlineStr">
+      <c r="AH28" s="77" t="n"/>
+      <c r="AI28" s="77" t="n"/>
+      <c r="AJ28" s="78" t="n"/>
+      <c r="AK28" s="97" t="inlineStr">
+        <is>
+          <t>上限あり</t>
+        </is>
+      </c>
+      <c r="AL28" s="77" t="n"/>
+      <c r="AM28" s="77" t="n"/>
+      <c r="AN28" s="77" t="n"/>
+      <c r="AO28" s="77" t="n"/>
+      <c r="AP28" s="78" t="n"/>
+      <c r="AQ28" s="97" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="AR28" s="77" t="n"/>
+      <c r="AS28" s="78" t="n"/>
+      <c r="AT28" s="97" t="inlineStr">
         <is>
           <t>有効</t>
         </is>
       </c>
-      <c r="AU9" s="27" t="n"/>
-      <c r="AV9" s="27" t="n"/>
-      <c r="AW9" s="27" t="n"/>
-      <c r="AX9" s="27" t="n"/>
-      <c r="AY9" s="27" t="n"/>
-      <c r="AZ9" s="27" t="n"/>
-      <c r="BA9" s="27" t="n"/>
-      <c r="BB9" s="27" t="n"/>
-      <c r="BC9" s="27" t="n"/>
-      <c r="BD9" s="28" t="n"/>
-    </row>
-    <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="22" t="n"/>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>月次勤怠</t>
-        </is>
-      </c>
-      <c r="L10" s="24" t="n"/>
-      <c r="N10" s="29" t="inlineStr">
-        <is>
-          <t>生理休暇</t>
-        </is>
-      </c>
-      <c r="O10" s="27" t="n"/>
-      <c r="P10" s="27" t="n"/>
-      <c r="Q10" s="27" t="n"/>
-      <c r="R10" s="27" t="n"/>
-      <c r="S10" s="27" t="n"/>
-      <c r="T10" s="27" t="n"/>
-      <c r="U10" s="28" t="n"/>
-      <c r="V10" s="29" t="inlineStr">
-        <is>
-          <t>労基法68条</t>
-        </is>
-      </c>
-      <c r="W10" s="27" t="n"/>
-      <c r="X10" s="27" t="n"/>
-      <c r="Y10" s="27" t="n"/>
-      <c r="Z10" s="27" t="n"/>
-      <c r="AA10" s="27" t="n"/>
-      <c r="AB10" s="27" t="n"/>
-      <c r="AC10" s="28" t="n"/>
-      <c r="AD10" s="29" t="inlineStr">
-        <is>
-          <t>無給可</t>
-        </is>
-      </c>
-      <c r="AE10" s="27" t="n"/>
-      <c r="AF10" s="27" t="n"/>
-      <c r="AG10" s="27" t="n"/>
-      <c r="AH10" s="27" t="n"/>
-      <c r="AI10" s="27" t="n"/>
-      <c r="AJ10" s="27" t="n"/>
-      <c r="AK10" s="28" t="n"/>
-      <c r="AL10" s="29" t="inlineStr">
-        <is>
-          <t>無制限</t>
-        </is>
-      </c>
-      <c r="AM10" s="27" t="n"/>
-      <c r="AN10" s="27" t="n"/>
-      <c r="AO10" s="27" t="n"/>
-      <c r="AP10" s="27" t="n"/>
-      <c r="AQ10" s="27" t="n"/>
-      <c r="AR10" s="27" t="n"/>
-      <c r="AS10" s="28" t="n"/>
-      <c r="AT10" s="29" t="inlineStr">
+      <c r="AU28" s="77" t="n"/>
+      <c r="AV28" s="77" t="n"/>
+      <c r="AW28" s="78" t="n"/>
+      <c r="AX28" s="97" t="inlineStr">
+        <is>
+          <t>編集</t>
+        </is>
+      </c>
+      <c r="AY28" s="77" t="n"/>
+      <c r="AZ28" s="78" t="n"/>
+      <c r="BA28" s="47" t="n"/>
+      <c r="BB28" s="47" t="n"/>
+      <c r="BC28" s="47" t="n"/>
+      <c r="BD28" s="47" t="n"/>
+      <c r="BE28" s="47" t="n"/>
+      <c r="BF28" s="47" t="n"/>
+      <c r="BG28" s="47" t="n"/>
+      <c r="BH28" s="47" t="n"/>
+    </row>
+    <row r="29" ht="17" customHeight="1">
+      <c r="A29" s="55" t="n"/>
+      <c r="B29" s="63" t="inlineStr">
+        <is>
+          <t>祝日・会社休日</t>
+        </is>
+      </c>
+      <c r="C29" s="57" t="n"/>
+      <c r="D29" s="57" t="n"/>
+      <c r="E29" s="57" t="n"/>
+      <c r="F29" s="57" t="n"/>
+      <c r="G29" s="57" t="n"/>
+      <c r="H29" s="57" t="n"/>
+      <c r="I29" s="57" t="n"/>
+      <c r="J29" s="57" t="n"/>
+      <c r="K29" s="57" t="n"/>
+      <c r="L29" s="58" t="n"/>
+      <c r="M29" s="47" t="n"/>
+      <c r="N29" s="47" t="n"/>
+      <c r="O29" s="96" t="inlineStr">
+        <is>
+          <t>特別休暇</t>
+        </is>
+      </c>
+      <c r="P29" s="77" t="n"/>
+      <c r="Q29" s="77" t="n"/>
+      <c r="R29" s="77" t="n"/>
+      <c r="S29" s="77" t="n"/>
+      <c r="T29" s="77" t="n"/>
+      <c r="U29" s="77" t="n"/>
+      <c r="V29" s="78" t="n"/>
+      <c r="W29" s="96" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X29" s="77" t="n"/>
+      <c r="Y29" s="77" t="n"/>
+      <c r="Z29" s="77" t="n"/>
+      <c r="AA29" s="77" t="n"/>
+      <c r="AB29" s="77" t="n"/>
+      <c r="AC29" s="77" t="n"/>
+      <c r="AD29" s="77" t="n"/>
+      <c r="AE29" s="77" t="n"/>
+      <c r="AF29" s="78" t="n"/>
+      <c r="AG29" s="97" t="inlineStr">
+        <is>
+          <t>有給</t>
+        </is>
+      </c>
+      <c r="AH29" s="77" t="n"/>
+      <c r="AI29" s="77" t="n"/>
+      <c r="AJ29" s="78" t="n"/>
+      <c r="AK29" s="97" t="inlineStr">
+        <is>
+          <t>上限あり</t>
+        </is>
+      </c>
+      <c r="AL29" s="77" t="n"/>
+      <c r="AM29" s="77" t="n"/>
+      <c r="AN29" s="77" t="n"/>
+      <c r="AO29" s="77" t="n"/>
+      <c r="AP29" s="78" t="n"/>
+      <c r="AQ29" s="97" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="AR29" s="77" t="n"/>
+      <c r="AS29" s="78" t="n"/>
+      <c r="AT29" s="97" t="inlineStr">
         <is>
           <t>有効</t>
         </is>
       </c>
-      <c r="AU10" s="27" t="n"/>
-      <c r="AV10" s="27" t="n"/>
-      <c r="AW10" s="27" t="n"/>
-      <c r="AX10" s="27" t="n"/>
-      <c r="AY10" s="27" t="n"/>
-      <c r="AZ10" s="27" t="n"/>
-      <c r="BA10" s="27" t="n"/>
-      <c r="BB10" s="27" t="n"/>
-      <c r="BC10" s="27" t="n"/>
-      <c r="BD10" s="28" t="n"/>
-    </row>
-    <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="22" t="n"/>
-      <c r="L11" s="24" t="n"/>
-    </row>
-    <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="22" t="n"/>
-      <c r="B12" s="23" t="inlineStr">
-        <is>
-          <t>休暇申請</t>
-        </is>
-      </c>
-      <c r="L12" s="24" t="n"/>
-      <c r="M12" s="25" t="inlineStr">
-        <is>
-          <t>②</t>
-        </is>
-      </c>
-      <c r="N12" s="30" t="inlineStr">
-        <is>
-          <t>名称</t>
-        </is>
-      </c>
-      <c r="O12" s="10" t="n"/>
-      <c r="P12" s="10" t="n"/>
-      <c r="Q12" s="10" t="n"/>
-      <c r="R12" s="10" t="n"/>
-      <c r="S12" s="10" t="n"/>
-      <c r="T12" s="10" t="n"/>
-      <c r="U12" s="11" t="n"/>
-      <c r="V12" s="31" t="inlineStr">
-        <is>
-          <t>年次有給休暇</t>
-        </is>
-      </c>
-      <c r="W12" s="10" t="n"/>
-      <c r="X12" s="10" t="n"/>
-      <c r="Y12" s="10" t="n"/>
-      <c r="Z12" s="10" t="n"/>
-      <c r="AA12" s="10" t="n"/>
-      <c r="AB12" s="10" t="n"/>
-      <c r="AC12" s="10" t="n"/>
-      <c r="AD12" s="10" t="n"/>
-      <c r="AE12" s="10" t="n"/>
-      <c r="AF12" s="10" t="n"/>
-      <c r="AG12" s="10" t="n"/>
-      <c r="AH12" s="10" t="n"/>
-      <c r="AI12" s="10" t="n"/>
-      <c r="AJ12" s="10" t="n"/>
-      <c r="AK12" s="10" t="n"/>
-      <c r="AL12" s="10" t="n"/>
-      <c r="AM12" s="10" t="n"/>
-      <c r="AN12" s="10" t="n"/>
-      <c r="AO12" s="10" t="n"/>
-      <c r="AP12" s="10" t="n"/>
-      <c r="AQ12" s="10" t="n"/>
-      <c r="AR12" s="11" t="n"/>
-    </row>
-    <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="22" t="n"/>
-      <c r="L13" s="24" t="n"/>
-      <c r="N13" s="15" t="n"/>
-      <c r="O13" s="16" t="n"/>
-      <c r="P13" s="16" t="n"/>
-      <c r="Q13" s="16" t="n"/>
-      <c r="R13" s="16" t="n"/>
-      <c r="S13" s="16" t="n"/>
-      <c r="T13" s="16" t="n"/>
-      <c r="U13" s="17" t="n"/>
-      <c r="V13" s="15" t="n"/>
-      <c r="W13" s="16" t="n"/>
-      <c r="X13" s="16" t="n"/>
-      <c r="Y13" s="16" t="n"/>
-      <c r="Z13" s="16" t="n"/>
-      <c r="AA13" s="16" t="n"/>
-      <c r="AB13" s="16" t="n"/>
-      <c r="AC13" s="16" t="n"/>
-      <c r="AD13" s="16" t="n"/>
-      <c r="AE13" s="16" t="n"/>
-      <c r="AF13" s="16" t="n"/>
-      <c r="AG13" s="16" t="n"/>
-      <c r="AH13" s="16" t="n"/>
-      <c r="AI13" s="16" t="n"/>
-      <c r="AJ13" s="16" t="n"/>
-      <c r="AK13" s="16" t="n"/>
-      <c r="AL13" s="16" t="n"/>
-      <c r="AM13" s="16" t="n"/>
-      <c r="AN13" s="16" t="n"/>
-      <c r="AO13" s="16" t="n"/>
-      <c r="AP13" s="16" t="n"/>
-      <c r="AQ13" s="16" t="n"/>
-      <c r="AR13" s="17" t="n"/>
-    </row>
-    <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="22" t="n"/>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t>申請一覧</t>
-        </is>
-      </c>
-      <c r="L14" s="24" t="n"/>
-    </row>
-    <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="22" t="n"/>
-      <c r="L15" s="24" t="n"/>
-      <c r="M15" s="25" t="inlineStr">
-        <is>
-          <t>③</t>
-        </is>
-      </c>
-      <c r="N15" s="30" t="inlineStr">
-        <is>
-          <t>法的根拠</t>
-        </is>
-      </c>
-      <c r="O15" s="10" t="n"/>
-      <c r="P15" s="10" t="n"/>
-      <c r="Q15" s="10" t="n"/>
-      <c r="R15" s="10" t="n"/>
-      <c r="S15" s="10" t="n"/>
-      <c r="T15" s="10" t="n"/>
-      <c r="U15" s="11" t="n"/>
-      <c r="V15" s="31" t="inlineStr">
-        <is>
-          <t>労働基準法第39条</t>
-        </is>
-      </c>
-      <c r="W15" s="10" t="n"/>
-      <c r="X15" s="10" t="n"/>
-      <c r="Y15" s="10" t="n"/>
-      <c r="Z15" s="10" t="n"/>
-      <c r="AA15" s="10" t="n"/>
-      <c r="AB15" s="10" t="n"/>
-      <c r="AC15" s="10" t="n"/>
-      <c r="AD15" s="10" t="n"/>
-      <c r="AE15" s="10" t="n"/>
-      <c r="AF15" s="10" t="n"/>
-      <c r="AG15" s="10" t="n"/>
-      <c r="AH15" s="10" t="n"/>
-      <c r="AI15" s="10" t="n"/>
-      <c r="AJ15" s="10" t="n"/>
-      <c r="AK15" s="10" t="n"/>
-      <c r="AL15" s="10" t="n"/>
-      <c r="AM15" s="10" t="n"/>
-      <c r="AN15" s="10" t="n"/>
-      <c r="AO15" s="10" t="n"/>
-      <c r="AP15" s="10" t="n"/>
-      <c r="AQ15" s="10" t="n"/>
-      <c r="AR15" s="11" t="n"/>
-    </row>
-    <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="22" t="n"/>
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>休暇残日数</t>
-        </is>
-      </c>
-      <c r="L16" s="24" t="n"/>
-      <c r="N16" s="15" t="n"/>
-      <c r="O16" s="16" t="n"/>
-      <c r="P16" s="16" t="n"/>
-      <c r="Q16" s="16" t="n"/>
-      <c r="R16" s="16" t="n"/>
-      <c r="S16" s="16" t="n"/>
-      <c r="T16" s="16" t="n"/>
-      <c r="U16" s="17" t="n"/>
-      <c r="V16" s="15" t="n"/>
-      <c r="W16" s="16" t="n"/>
-      <c r="X16" s="16" t="n"/>
-      <c r="Y16" s="16" t="n"/>
-      <c r="Z16" s="16" t="n"/>
-      <c r="AA16" s="16" t="n"/>
-      <c r="AB16" s="16" t="n"/>
-      <c r="AC16" s="16" t="n"/>
-      <c r="AD16" s="16" t="n"/>
-      <c r="AE16" s="16" t="n"/>
-      <c r="AF16" s="16" t="n"/>
-      <c r="AG16" s="16" t="n"/>
-      <c r="AH16" s="16" t="n"/>
-      <c r="AI16" s="16" t="n"/>
-      <c r="AJ16" s="16" t="n"/>
-      <c r="AK16" s="16" t="n"/>
-      <c r="AL16" s="16" t="n"/>
-      <c r="AM16" s="16" t="n"/>
-      <c r="AN16" s="16" t="n"/>
-      <c r="AO16" s="16" t="n"/>
-      <c r="AP16" s="16" t="n"/>
-      <c r="AQ16" s="16" t="n"/>
-      <c r="AR16" s="17" t="n"/>
-    </row>
-    <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="22" t="n"/>
-      <c r="L17" s="24" t="n"/>
-    </row>
-    <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="22" t="n"/>
-      <c r="B18" s="32" t="n"/>
-      <c r="C18" s="32" t="n"/>
-      <c r="D18" s="32" t="n"/>
-      <c r="E18" s="32" t="n"/>
-      <c r="F18" s="32" t="n"/>
-      <c r="G18" s="32" t="n"/>
-      <c r="H18" s="32" t="n"/>
-      <c r="I18" s="32" t="n"/>
-      <c r="J18" s="32" t="n"/>
-      <c r="K18" s="32" t="n"/>
-      <c r="L18" s="24" t="n"/>
-      <c r="M18" s="25" t="inlineStr">
-        <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="N18" s="30" t="inlineStr">
-        <is>
-          <t>有給・無給</t>
-        </is>
-      </c>
-      <c r="O18" s="10" t="n"/>
-      <c r="P18" s="10" t="n"/>
-      <c r="Q18" s="10" t="n"/>
-      <c r="R18" s="10" t="n"/>
-      <c r="S18" s="10" t="n"/>
-      <c r="T18" s="10" t="n"/>
-      <c r="U18" s="11" t="n"/>
-      <c r="V18" s="33" t="inlineStr">
-        <is>
-          <t>(●) 有給　( ) 無給可</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="17" customHeight="1">
-      <c r="A19" s="22" t="n"/>
-      <c r="B19" s="32" t="n"/>
-      <c r="C19" s="32" t="n"/>
-      <c r="D19" s="32" t="n"/>
-      <c r="E19" s="32" t="n"/>
-      <c r="F19" s="32" t="n"/>
-      <c r="G19" s="32" t="n"/>
-      <c r="H19" s="32" t="n"/>
-      <c r="I19" s="32" t="n"/>
-      <c r="J19" s="32" t="n"/>
-      <c r="K19" s="32" t="n"/>
-      <c r="L19" s="24" t="n"/>
-      <c r="N19" s="15" t="n"/>
-      <c r="O19" s="16" t="n"/>
-      <c r="P19" s="16" t="n"/>
-      <c r="Q19" s="16" t="n"/>
-      <c r="R19" s="16" t="n"/>
-      <c r="S19" s="16" t="n"/>
-      <c r="T19" s="16" t="n"/>
-      <c r="U19" s="17" t="n"/>
-    </row>
-    <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="22" t="n"/>
-      <c r="B20" s="32" t="n"/>
-      <c r="C20" s="32" t="n"/>
-      <c r="D20" s="32" t="n"/>
-      <c r="E20" s="32" t="n"/>
-      <c r="F20" s="32" t="n"/>
-      <c r="G20" s="32" t="n"/>
-      <c r="H20" s="32" t="n"/>
-      <c r="I20" s="32" t="n"/>
-      <c r="J20" s="32" t="n"/>
-      <c r="K20" s="32" t="n"/>
-      <c r="L20" s="24" t="n"/>
-    </row>
-    <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="22" t="n"/>
-      <c r="B21" s="32" t="n"/>
-      <c r="C21" s="32" t="n"/>
-      <c r="D21" s="32" t="n"/>
-      <c r="E21" s="32" t="n"/>
-      <c r="F21" s="32" t="n"/>
-      <c r="G21" s="32" t="n"/>
-      <c r="H21" s="32" t="n"/>
-      <c r="I21" s="32" t="n"/>
-      <c r="J21" s="32" t="n"/>
-      <c r="K21" s="32" t="n"/>
-      <c r="L21" s="24" t="n"/>
-      <c r="M21" s="25" t="inlineStr">
-        <is>
-          <t>⑤</t>
-        </is>
-      </c>
-      <c r="N21" s="30" t="inlineStr">
-        <is>
-          <t>日数ルール</t>
-        </is>
-      </c>
-      <c r="O21" s="10" t="n"/>
-      <c r="P21" s="10" t="n"/>
-      <c r="Q21" s="10" t="n"/>
-      <c r="R21" s="10" t="n"/>
-      <c r="S21" s="10" t="n"/>
-      <c r="T21" s="10" t="n"/>
-      <c r="U21" s="11" t="n"/>
-      <c r="V21" s="31" t="inlineStr">
-        <is>
-          <t>▼ 上限付き</t>
-        </is>
-      </c>
-      <c r="W21" s="10" t="n"/>
-      <c r="X21" s="10" t="n"/>
-      <c r="Y21" s="10" t="n"/>
-      <c r="Z21" s="10" t="n"/>
-      <c r="AA21" s="10" t="n"/>
-      <c r="AB21" s="10" t="n"/>
-      <c r="AC21" s="10" t="n"/>
-      <c r="AD21" s="10" t="n"/>
-      <c r="AE21" s="10" t="n"/>
-      <c r="AF21" s="10" t="n"/>
-      <c r="AG21" s="10" t="n"/>
-      <c r="AH21" s="10" t="n"/>
-      <c r="AI21" s="10" t="n"/>
-      <c r="AJ21" s="10" t="n"/>
-      <c r="AK21" s="10" t="n"/>
-      <c r="AL21" s="10" t="n"/>
-      <c r="AM21" s="10" t="n"/>
-      <c r="AN21" s="10" t="n"/>
-      <c r="AO21" s="10" t="n"/>
-      <c r="AP21" s="10" t="n"/>
-      <c r="AQ21" s="10" t="n"/>
-      <c r="AR21" s="11" t="n"/>
-    </row>
-    <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="22" t="n"/>
-      <c r="B22" s="32" t="n"/>
-      <c r="C22" s="32" t="n"/>
-      <c r="D22" s="32" t="n"/>
-      <c r="E22" s="32" t="n"/>
-      <c r="F22" s="32" t="n"/>
-      <c r="G22" s="32" t="n"/>
-      <c r="H22" s="32" t="n"/>
-      <c r="I22" s="32" t="n"/>
-      <c r="J22" s="32" t="n"/>
-      <c r="K22" s="32" t="n"/>
-      <c r="L22" s="24" t="n"/>
-      <c r="N22" s="15" t="n"/>
-      <c r="O22" s="16" t="n"/>
-      <c r="P22" s="16" t="n"/>
-      <c r="Q22" s="16" t="n"/>
-      <c r="R22" s="16" t="n"/>
-      <c r="S22" s="16" t="n"/>
-      <c r="T22" s="16" t="n"/>
-      <c r="U22" s="17" t="n"/>
-      <c r="V22" s="15" t="n"/>
-      <c r="W22" s="16" t="n"/>
-      <c r="X22" s="16" t="n"/>
-      <c r="Y22" s="16" t="n"/>
-      <c r="Z22" s="16" t="n"/>
-      <c r="AA22" s="16" t="n"/>
-      <c r="AB22" s="16" t="n"/>
-      <c r="AC22" s="16" t="n"/>
-      <c r="AD22" s="16" t="n"/>
-      <c r="AE22" s="16" t="n"/>
-      <c r="AF22" s="16" t="n"/>
-      <c r="AG22" s="16" t="n"/>
-      <c r="AH22" s="16" t="n"/>
-      <c r="AI22" s="16" t="n"/>
-      <c r="AJ22" s="16" t="n"/>
-      <c r="AK22" s="16" t="n"/>
-      <c r="AL22" s="16" t="n"/>
-      <c r="AM22" s="16" t="n"/>
-      <c r="AN22" s="16" t="n"/>
-      <c r="AO22" s="16" t="n"/>
-      <c r="AP22" s="16" t="n"/>
-      <c r="AQ22" s="16" t="n"/>
-      <c r="AR22" s="17" t="n"/>
-    </row>
-    <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="22" t="n"/>
-      <c r="B23" s="32" t="n"/>
-      <c r="C23" s="32" t="n"/>
-      <c r="D23" s="32" t="n"/>
-      <c r="E23" s="32" t="n"/>
-      <c r="F23" s="32" t="n"/>
-      <c r="G23" s="32" t="n"/>
-      <c r="H23" s="32" t="n"/>
-      <c r="I23" s="32" t="n"/>
-      <c r="J23" s="32" t="n"/>
-      <c r="K23" s="32" t="n"/>
-      <c r="L23" s="24" t="n"/>
-    </row>
-    <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="22" t="n"/>
-      <c r="B24" s="32" t="n"/>
-      <c r="C24" s="32" t="n"/>
-      <c r="D24" s="32" t="n"/>
-      <c r="E24" s="32" t="n"/>
-      <c r="F24" s="32" t="n"/>
-      <c r="G24" s="32" t="n"/>
-      <c r="H24" s="32" t="n"/>
-      <c r="I24" s="32" t="n"/>
-      <c r="J24" s="32" t="n"/>
-      <c r="K24" s="32" t="n"/>
-      <c r="L24" s="24" t="n"/>
-      <c r="M24" s="25" t="inlineStr">
-        <is>
-          <t>⑥</t>
-        </is>
-      </c>
-      <c r="N24" s="30" t="inlineStr">
-        <is>
-          <t>半日取得可</t>
-        </is>
-      </c>
-      <c r="O24" s="10" t="n"/>
-      <c r="P24" s="10" t="n"/>
-      <c r="Q24" s="10" t="n"/>
-      <c r="R24" s="10" t="n"/>
-      <c r="S24" s="10" t="n"/>
-      <c r="T24" s="10" t="n"/>
-      <c r="U24" s="11" t="n"/>
-      <c r="V24" s="33" t="inlineStr">
-        <is>
-          <t>[ ]</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="22" t="n"/>
-      <c r="B25" s="32" t="n"/>
-      <c r="C25" s="32" t="n"/>
-      <c r="D25" s="32" t="n"/>
-      <c r="E25" s="32" t="n"/>
-      <c r="F25" s="32" t="n"/>
-      <c r="G25" s="32" t="n"/>
-      <c r="H25" s="32" t="n"/>
-      <c r="I25" s="32" t="n"/>
-      <c r="J25" s="32" t="n"/>
-      <c r="K25" s="32" t="n"/>
-      <c r="L25" s="24" t="n"/>
-      <c r="N25" s="15" t="n"/>
-      <c r="O25" s="16" t="n"/>
-      <c r="P25" s="16" t="n"/>
-      <c r="Q25" s="16" t="n"/>
-      <c r="R25" s="16" t="n"/>
-      <c r="S25" s="16" t="n"/>
-      <c r="T25" s="16" t="n"/>
-      <c r="U25" s="17" t="n"/>
-    </row>
-    <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="22" t="n"/>
-      <c r="B26" s="32" t="n"/>
-      <c r="C26" s="32" t="n"/>
-      <c r="D26" s="32" t="n"/>
-      <c r="E26" s="32" t="n"/>
-      <c r="F26" s="32" t="n"/>
-      <c r="G26" s="32" t="n"/>
-      <c r="H26" s="32" t="n"/>
-      <c r="I26" s="32" t="n"/>
-      <c r="J26" s="32" t="n"/>
-      <c r="K26" s="32" t="n"/>
-      <c r="L26" s="24" t="n"/>
-    </row>
-    <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="22" t="n"/>
-      <c r="B27" s="32" t="n"/>
-      <c r="C27" s="32" t="n"/>
-      <c r="D27" s="32" t="n"/>
-      <c r="E27" s="32" t="n"/>
-      <c r="F27" s="32" t="n"/>
-      <c r="G27" s="32" t="n"/>
-      <c r="H27" s="32" t="n"/>
-      <c r="I27" s="32" t="n"/>
-      <c r="J27" s="32" t="n"/>
-      <c r="K27" s="32" t="n"/>
-      <c r="L27" s="24" t="n"/>
-      <c r="M27" s="25" t="inlineStr">
-        <is>
-          <t>⑦</t>
-        </is>
-      </c>
-      <c r="N27" s="30" t="inlineStr">
-        <is>
-          <t>有効</t>
-        </is>
-      </c>
-      <c r="O27" s="10" t="n"/>
-      <c r="P27" s="10" t="n"/>
-      <c r="Q27" s="10" t="n"/>
-      <c r="R27" s="10" t="n"/>
-      <c r="S27" s="10" t="n"/>
-      <c r="T27" s="10" t="n"/>
-      <c r="U27" s="11" t="n"/>
-      <c r="V27" s="33" t="inlineStr">
-        <is>
-          <t>[ ]</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="17" customHeight="1">
-      <c r="A28" s="22" t="n"/>
-      <c r="B28" s="32" t="n"/>
-      <c r="C28" s="32" t="n"/>
-      <c r="D28" s="32" t="n"/>
-      <c r="E28" s="32" t="n"/>
-      <c r="F28" s="32" t="n"/>
-      <c r="G28" s="32" t="n"/>
-      <c r="H28" s="32" t="n"/>
-      <c r="I28" s="32" t="n"/>
-      <c r="J28" s="32" t="n"/>
-      <c r="K28" s="32" t="n"/>
-      <c r="L28" s="24" t="n"/>
-      <c r="N28" s="15" t="n"/>
-      <c r="O28" s="16" t="n"/>
-      <c r="P28" s="16" t="n"/>
-      <c r="Q28" s="16" t="n"/>
-      <c r="R28" s="16" t="n"/>
-      <c r="S28" s="16" t="n"/>
-      <c r="T28" s="16" t="n"/>
-      <c r="U28" s="17" t="n"/>
-    </row>
-    <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="22" t="n"/>
-      <c r="B29" s="32" t="n"/>
-      <c r="C29" s="32" t="n"/>
-      <c r="D29" s="32" t="n"/>
-      <c r="E29" s="32" t="n"/>
-      <c r="F29" s="32" t="n"/>
-      <c r="G29" s="32" t="n"/>
-      <c r="H29" s="32" t="n"/>
-      <c r="I29" s="32" t="n"/>
-      <c r="J29" s="32" t="n"/>
-      <c r="K29" s="32" t="n"/>
-      <c r="L29" s="24" t="n"/>
+      <c r="AU29" s="77" t="n"/>
+      <c r="AV29" s="77" t="n"/>
+      <c r="AW29" s="78" t="n"/>
+      <c r="AX29" s="97" t="inlineStr">
+        <is>
+          <t>編集</t>
+        </is>
+      </c>
+      <c r="AY29" s="77" t="n"/>
+      <c r="AZ29" s="78" t="n"/>
+      <c r="BA29" s="47" t="n"/>
+      <c r="BB29" s="47" t="n"/>
+      <c r="BC29" s="47" t="n"/>
+      <c r="BD29" s="47" t="n"/>
+      <c r="BE29" s="47" t="n"/>
+      <c r="BF29" s="47" t="n"/>
+      <c r="BG29" s="47" t="n"/>
+      <c r="BH29" s="47" t="n"/>
     </row>
     <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="22" t="n"/>
-      <c r="B30" s="32" t="n"/>
-      <c r="C30" s="32" t="n"/>
-      <c r="D30" s="32" t="n"/>
-      <c r="E30" s="32" t="n"/>
-      <c r="F30" s="32" t="n"/>
-      <c r="G30" s="32" t="n"/>
-      <c r="H30" s="32" t="n"/>
-      <c r="I30" s="32" t="n"/>
-      <c r="J30" s="32" t="n"/>
-      <c r="K30" s="32" t="n"/>
-      <c r="L30" s="24" t="n"/>
-      <c r="M30" s="25" t="inlineStr">
-        <is>
-          <t>⑧</t>
-        </is>
-      </c>
-      <c r="N30" s="34" t="inlineStr">
-        <is>
-          <t>新規</t>
-        </is>
-      </c>
-      <c r="O30" s="10" t="n"/>
-      <c r="P30" s="10" t="n"/>
-      <c r="Q30" s="10" t="n"/>
-      <c r="R30" s="10" t="n"/>
-      <c r="S30" s="10" t="n"/>
-      <c r="T30" s="10" t="n"/>
-      <c r="U30" s="10" t="n"/>
-      <c r="V30" s="10" t="n"/>
-      <c r="W30" s="10" t="n"/>
-      <c r="X30" s="10" t="n"/>
-      <c r="Y30" s="11" t="n"/>
-      <c r="AB30" s="25" t="inlineStr">
-        <is>
-          <t>⑨</t>
-        </is>
-      </c>
-      <c r="AC30" s="34" t="inlineStr">
-        <is>
-          <t>保存</t>
-        </is>
-      </c>
-      <c r="AD30" s="10" t="n"/>
-      <c r="AE30" s="10" t="n"/>
-      <c r="AF30" s="10" t="n"/>
-      <c r="AG30" s="10" t="n"/>
-      <c r="AH30" s="10" t="n"/>
-      <c r="AI30" s="10" t="n"/>
-      <c r="AJ30" s="10" t="n"/>
-      <c r="AK30" s="10" t="n"/>
-      <c r="AL30" s="10" t="n"/>
-      <c r="AM30" s="10" t="n"/>
-      <c r="AN30" s="11" t="n"/>
+      <c r="A30" s="55" t="n"/>
+      <c r="B30" s="57" t="n"/>
+      <c r="C30" s="57" t="n"/>
+      <c r="D30" s="57" t="n"/>
+      <c r="E30" s="57" t="n"/>
+      <c r="F30" s="57" t="n"/>
+      <c r="G30" s="57" t="n"/>
+      <c r="H30" s="57" t="n"/>
+      <c r="I30" s="57" t="n"/>
+      <c r="J30" s="57" t="n"/>
+      <c r="K30" s="57" t="n"/>
+      <c r="L30" s="58" t="n"/>
+      <c r="M30" s="47" t="n"/>
+      <c r="N30" s="47" t="n"/>
+      <c r="O30" s="96" t="inlineStr">
+        <is>
+          <t>欠勤</t>
+        </is>
+      </c>
+      <c r="P30" s="77" t="n"/>
+      <c r="Q30" s="77" t="n"/>
+      <c r="R30" s="77" t="n"/>
+      <c r="S30" s="77" t="n"/>
+      <c r="T30" s="77" t="n"/>
+      <c r="U30" s="77" t="n"/>
+      <c r="V30" s="78" t="n"/>
+      <c r="W30" s="96" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X30" s="77" t="n"/>
+      <c r="Y30" s="77" t="n"/>
+      <c r="Z30" s="77" t="n"/>
+      <c r="AA30" s="77" t="n"/>
+      <c r="AB30" s="77" t="n"/>
+      <c r="AC30" s="77" t="n"/>
+      <c r="AD30" s="77" t="n"/>
+      <c r="AE30" s="77" t="n"/>
+      <c r="AF30" s="78" t="n"/>
+      <c r="AG30" s="97" t="inlineStr">
+        <is>
+          <t>無給</t>
+        </is>
+      </c>
+      <c r="AH30" s="77" t="n"/>
+      <c r="AI30" s="77" t="n"/>
+      <c r="AJ30" s="78" t="n"/>
+      <c r="AK30" s="97" t="inlineStr">
+        <is>
+          <t>上限なし</t>
+        </is>
+      </c>
+      <c r="AL30" s="77" t="n"/>
+      <c r="AM30" s="77" t="n"/>
+      <c r="AN30" s="77" t="n"/>
+      <c r="AO30" s="77" t="n"/>
+      <c r="AP30" s="78" t="n"/>
+      <c r="AQ30" s="97" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="AR30" s="77" t="n"/>
+      <c r="AS30" s="78" t="n"/>
+      <c r="AT30" s="97" t="inlineStr">
+        <is>
+          <t>無効</t>
+        </is>
+      </c>
+      <c r="AU30" s="77" t="n"/>
+      <c r="AV30" s="77" t="n"/>
+      <c r="AW30" s="78" t="n"/>
+      <c r="AX30" s="97" t="inlineStr">
+        <is>
+          <t>編集</t>
+        </is>
+      </c>
+      <c r="AY30" s="77" t="n"/>
+      <c r="AZ30" s="78" t="n"/>
+      <c r="BA30" s="47" t="n"/>
+      <c r="BB30" s="47" t="n"/>
+      <c r="BC30" s="47" t="n"/>
+      <c r="BD30" s="47" t="n"/>
+      <c r="BE30" s="47" t="n"/>
+      <c r="BF30" s="47" t="n"/>
+      <c r="BG30" s="47" t="n"/>
+      <c r="BH30" s="47" t="n"/>
     </row>
     <row r="31" ht="17" customHeight="1">
-      <c r="A31" s="22" t="n"/>
-      <c r="B31" s="32" t="n"/>
-      <c r="C31" s="32" t="n"/>
-      <c r="D31" s="32" t="n"/>
-      <c r="E31" s="32" t="n"/>
-      <c r="F31" s="32" t="n"/>
-      <c r="G31" s="32" t="n"/>
-      <c r="H31" s="32" t="n"/>
-      <c r="I31" s="32" t="n"/>
-      <c r="J31" s="32" t="n"/>
-      <c r="K31" s="32" t="n"/>
-      <c r="L31" s="24" t="n"/>
-      <c r="N31" s="13" t="n"/>
-      <c r="Y31" s="14" t="n"/>
-      <c r="AC31" s="13" t="n"/>
-      <c r="AN31" s="14" t="n"/>
+      <c r="A31" s="55" t="n"/>
+      <c r="B31" s="81" t="n"/>
+      <c r="C31" s="81" t="n"/>
+      <c r="D31" s="81" t="n"/>
+      <c r="E31" s="81" t="n"/>
+      <c r="F31" s="81" t="n"/>
+      <c r="G31" s="81" t="n"/>
+      <c r="H31" s="81" t="n"/>
+      <c r="I31" s="81" t="n"/>
+      <c r="J31" s="81" t="n"/>
+      <c r="K31" s="81" t="n"/>
+      <c r="L31" s="58" t="n"/>
+      <c r="M31" s="47" t="n"/>
+      <c r="N31" s="47" t="n"/>
+      <c r="O31" s="47" t="n"/>
+      <c r="P31" s="47" t="n"/>
+      <c r="Q31" s="47" t="n"/>
+      <c r="R31" s="47" t="n"/>
+      <c r="S31" s="47" t="n"/>
+      <c r="T31" s="47" t="n"/>
+      <c r="U31" s="47" t="n"/>
+      <c r="V31" s="47" t="n"/>
+      <c r="W31" s="47" t="n"/>
+      <c r="X31" s="47" t="n"/>
+      <c r="Y31" s="47" t="n"/>
+      <c r="Z31" s="47" t="n"/>
+      <c r="AA31" s="47" t="n"/>
+      <c r="AB31" s="47" t="n"/>
+      <c r="AC31" s="47" t="n"/>
+      <c r="AD31" s="47" t="n"/>
+      <c r="AE31" s="47" t="n"/>
+      <c r="AF31" s="47" t="n"/>
+      <c r="AG31" s="47" t="n"/>
+      <c r="AH31" s="47" t="n"/>
+      <c r="AI31" s="47" t="n"/>
+      <c r="AJ31" s="47" t="n"/>
+      <c r="AK31" s="47" t="n"/>
+      <c r="AL31" s="47" t="n"/>
+      <c r="AM31" s="47" t="n"/>
+      <c r="AN31" s="47" t="n"/>
+      <c r="AO31" s="47" t="n"/>
+      <c r="AP31" s="47" t="n"/>
+      <c r="AQ31" s="47" t="n"/>
+      <c r="AR31" s="47" t="n"/>
+      <c r="AS31" s="47" t="n"/>
+      <c r="AT31" s="47" t="n"/>
+      <c r="AU31" s="47" t="n"/>
+      <c r="AV31" s="47" t="n"/>
+      <c r="AW31" s="47" t="n"/>
+      <c r="AX31" s="47" t="n"/>
+      <c r="AY31" s="47" t="n"/>
+      <c r="AZ31" s="47" t="n"/>
+      <c r="BA31" s="47" t="n"/>
+      <c r="BB31" s="47" t="n"/>
+      <c r="BC31" s="47" t="n"/>
+      <c r="BD31" s="47" t="n"/>
+      <c r="BE31" s="47" t="n"/>
+      <c r="BF31" s="47" t="n"/>
+      <c r="BG31" s="47" t="n"/>
+      <c r="BH31" s="47" t="n"/>
     </row>
     <row r="32" ht="17" customHeight="1">
-      <c r="A32" s="22" t="n"/>
-      <c r="B32" s="32" t="n"/>
-      <c r="C32" s="32" t="n"/>
-      <c r="D32" s="32" t="n"/>
-      <c r="E32" s="32" t="n"/>
-      <c r="F32" s="32" t="n"/>
-      <c r="G32" s="32" t="n"/>
-      <c r="H32" s="32" t="n"/>
-      <c r="I32" s="32" t="n"/>
-      <c r="J32" s="32" t="n"/>
-      <c r="K32" s="32" t="n"/>
-      <c r="L32" s="24" t="n"/>
-      <c r="N32" s="15" t="n"/>
-      <c r="O32" s="16" t="n"/>
-      <c r="P32" s="16" t="n"/>
-      <c r="Q32" s="16" t="n"/>
-      <c r="R32" s="16" t="n"/>
-      <c r="S32" s="16" t="n"/>
-      <c r="T32" s="16" t="n"/>
-      <c r="U32" s="16" t="n"/>
-      <c r="V32" s="16" t="n"/>
-      <c r="W32" s="16" t="n"/>
-      <c r="X32" s="16" t="n"/>
-      <c r="Y32" s="17" t="n"/>
-      <c r="AC32" s="15" t="n"/>
-      <c r="AD32" s="16" t="n"/>
-      <c r="AE32" s="16" t="n"/>
-      <c r="AF32" s="16" t="n"/>
-      <c r="AG32" s="16" t="n"/>
-      <c r="AH32" s="16" t="n"/>
-      <c r="AI32" s="16" t="n"/>
-      <c r="AJ32" s="16" t="n"/>
-      <c r="AK32" s="16" t="n"/>
-      <c r="AL32" s="16" t="n"/>
-      <c r="AM32" s="16" t="n"/>
-      <c r="AN32" s="17" t="n"/>
+      <c r="A32" s="55" t="n"/>
+      <c r="B32" s="81" t="n"/>
+      <c r="C32" s="81" t="n"/>
+      <c r="D32" s="81" t="n"/>
+      <c r="E32" s="81" t="n"/>
+      <c r="F32" s="81" t="n"/>
+      <c r="G32" s="81" t="n"/>
+      <c r="H32" s="81" t="n"/>
+      <c r="I32" s="81" t="n"/>
+      <c r="J32" s="81" t="n"/>
+      <c r="K32" s="81" t="n"/>
+      <c r="L32" s="58" t="n"/>
+      <c r="M32" s="47" t="n"/>
+      <c r="N32" s="47" t="n"/>
+      <c r="O32" s="47" t="n"/>
+      <c r="P32" s="47" t="n"/>
+      <c r="Q32" s="47" t="n"/>
+      <c r="R32" s="47" t="n"/>
+      <c r="S32" s="47" t="n"/>
+      <c r="T32" s="47" t="n"/>
+      <c r="U32" s="47" t="n"/>
+      <c r="V32" s="47" t="n"/>
+      <c r="W32" s="47" t="n"/>
+      <c r="X32" s="47" t="n"/>
+      <c r="Y32" s="47" t="n"/>
+      <c r="Z32" s="47" t="n"/>
+      <c r="AA32" s="47" t="n"/>
+      <c r="AB32" s="47" t="n"/>
+      <c r="AC32" s="47" t="n"/>
+      <c r="AD32" s="47" t="n"/>
+      <c r="AE32" s="47" t="n"/>
+      <c r="AF32" s="47" t="n"/>
+      <c r="AG32" s="47" t="n"/>
+      <c r="AH32" s="47" t="n"/>
+      <c r="AI32" s="47" t="n"/>
+      <c r="AJ32" s="47" t="n"/>
+      <c r="AK32" s="47" t="n"/>
+      <c r="AL32" s="47" t="n"/>
+      <c r="AM32" s="47" t="n"/>
+      <c r="AN32" s="47" t="n"/>
+      <c r="AO32" s="47" t="n"/>
+      <c r="AP32" s="47" t="n"/>
+      <c r="AQ32" s="47" t="n"/>
+      <c r="AR32" s="47" t="n"/>
+      <c r="AS32" s="47" t="n"/>
+      <c r="AT32" s="47" t="n"/>
+      <c r="AU32" s="47" t="n"/>
+      <c r="AV32" s="47" t="n"/>
+      <c r="AW32" s="47" t="n"/>
+      <c r="AX32" s="47" t="n"/>
+      <c r="AY32" s="47" t="n"/>
+      <c r="AZ32" s="47" t="n"/>
+      <c r="BA32" s="47" t="n"/>
+      <c r="BB32" s="47" t="n"/>
+      <c r="BC32" s="47" t="n"/>
+      <c r="BD32" s="47" t="n"/>
+      <c r="BE32" s="47" t="n"/>
+      <c r="BF32" s="47" t="n"/>
+      <c r="BG32" s="47" t="n"/>
+      <c r="BH32" s="47" t="n"/>
     </row>
     <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="22" t="n"/>
-      <c r="B33" s="32" t="n"/>
-      <c r="C33" s="32" t="n"/>
-      <c r="D33" s="32" t="n"/>
-      <c r="E33" s="32" t="n"/>
-      <c r="F33" s="32" t="n"/>
-      <c r="G33" s="32" t="n"/>
-      <c r="H33" s="32" t="n"/>
-      <c r="I33" s="32" t="n"/>
-      <c r="J33" s="32" t="n"/>
-      <c r="K33" s="32" t="n"/>
-      <c r="L33" s="24" t="n"/>
+      <c r="A33" s="55" t="n"/>
+      <c r="B33" s="81" t="n"/>
+      <c r="C33" s="81" t="n"/>
+      <c r="D33" s="81" t="n"/>
+      <c r="E33" s="81" t="n"/>
+      <c r="F33" s="81" t="n"/>
+      <c r="G33" s="81" t="n"/>
+      <c r="H33" s="81" t="n"/>
+      <c r="I33" s="81" t="n"/>
+      <c r="J33" s="81" t="n"/>
+      <c r="K33" s="81" t="n"/>
+      <c r="L33" s="58" t="n"/>
+      <c r="M33" s="47" t="n"/>
+      <c r="N33" s="47" t="n"/>
+      <c r="O33" s="47" t="n"/>
+      <c r="P33" s="47" t="n"/>
+      <c r="Q33" s="47" t="n"/>
+      <c r="R33" s="47" t="n"/>
+      <c r="S33" s="47" t="n"/>
+      <c r="T33" s="47" t="n"/>
+      <c r="U33" s="47" t="n"/>
+      <c r="V33" s="47" t="n"/>
+      <c r="W33" s="47" t="n"/>
+      <c r="X33" s="47" t="n"/>
+      <c r="Y33" s="47" t="n"/>
+      <c r="Z33" s="47" t="n"/>
+      <c r="AA33" s="47" t="n"/>
+      <c r="AB33" s="47" t="n"/>
+      <c r="AC33" s="47" t="n"/>
+      <c r="AD33" s="47" t="n"/>
+      <c r="AE33" s="47" t="n"/>
+      <c r="AF33" s="47" t="n"/>
+      <c r="AG33" s="47" t="n"/>
+      <c r="AH33" s="47" t="n"/>
+      <c r="AI33" s="47" t="n"/>
+      <c r="AJ33" s="47" t="n"/>
+      <c r="AK33" s="47" t="n"/>
+      <c r="AL33" s="47" t="n"/>
+      <c r="AM33" s="47" t="n"/>
+      <c r="AN33" s="47" t="n"/>
+      <c r="AO33" s="47" t="n"/>
+      <c r="AP33" s="47" t="n"/>
+      <c r="AQ33" s="47" t="n"/>
+      <c r="AR33" s="47" t="n"/>
+      <c r="AS33" s="47" t="n"/>
+      <c r="AT33" s="47" t="n"/>
+      <c r="AU33" s="47" t="n"/>
+      <c r="AV33" s="47" t="n"/>
+      <c r="AW33" s="47" t="n"/>
+      <c r="AX33" s="47" t="n"/>
+      <c r="AY33" s="47" t="n"/>
+      <c r="AZ33" s="47" t="n"/>
+      <c r="BA33" s="47" t="n"/>
+      <c r="BB33" s="47" t="n"/>
+      <c r="BC33" s="47" t="n"/>
+      <c r="BD33" s="47" t="n"/>
+      <c r="BE33" s="47" t="n"/>
+      <c r="BF33" s="47" t="n"/>
+      <c r="BG33" s="47" t="n"/>
+      <c r="BH33" s="47" t="n"/>
     </row>
     <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="22" t="n"/>
-      <c r="B34" s="32" t="n"/>
-      <c r="C34" s="32" t="n"/>
-      <c r="D34" s="32" t="n"/>
-      <c r="E34" s="32" t="n"/>
-      <c r="F34" s="32" t="n"/>
-      <c r="G34" s="32" t="n"/>
-      <c r="H34" s="32" t="n"/>
-      <c r="I34" s="32" t="n"/>
-      <c r="J34" s="32" t="n"/>
-      <c r="K34" s="32" t="n"/>
-      <c r="L34" s="24" t="n"/>
+      <c r="A34" s="55" t="n"/>
+      <c r="B34" s="81" t="n"/>
+      <c r="C34" s="81" t="n"/>
+      <c r="D34" s="81" t="n"/>
+      <c r="E34" s="81" t="n"/>
+      <c r="F34" s="81" t="n"/>
+      <c r="G34" s="81" t="n"/>
+      <c r="H34" s="81" t="n"/>
+      <c r="I34" s="81" t="n"/>
+      <c r="J34" s="81" t="n"/>
+      <c r="K34" s="81" t="n"/>
+      <c r="L34" s="58" t="n"/>
+      <c r="M34" s="47" t="n"/>
+      <c r="N34" s="47" t="n"/>
+      <c r="O34" s="59" t="inlineStr">
+        <is>
+          <t>⑩</t>
+        </is>
+      </c>
+      <c r="P34" s="98" t="inlineStr">
+        <is>
+          <t>休暇種別「特別休暇」を更新しました。</t>
+        </is>
+      </c>
+      <c r="Q34" s="99" t="n"/>
+      <c r="R34" s="99" t="n"/>
+      <c r="S34" s="99" t="n"/>
+      <c r="T34" s="99" t="n"/>
+      <c r="U34" s="99" t="n"/>
+      <c r="V34" s="99" t="n"/>
+      <c r="W34" s="99" t="n"/>
+      <c r="X34" s="99" t="n"/>
+      <c r="Y34" s="99" t="n"/>
+      <c r="Z34" s="99" t="n"/>
+      <c r="AA34" s="99" t="n"/>
+      <c r="AB34" s="99" t="n"/>
+      <c r="AC34" s="99" t="n"/>
+      <c r="AD34" s="99" t="n"/>
+      <c r="AE34" s="99" t="n"/>
+      <c r="AF34" s="99" t="n"/>
+      <c r="AG34" s="99" t="n"/>
+      <c r="AH34" s="99" t="n"/>
+      <c r="AI34" s="99" t="n"/>
+      <c r="AJ34" s="99" t="n"/>
+      <c r="AK34" s="99" t="n"/>
+      <c r="AL34" s="99" t="n"/>
+      <c r="AM34" s="99" t="n"/>
+      <c r="AN34" s="99" t="n"/>
+      <c r="AO34" s="99" t="n"/>
+      <c r="AP34" s="99" t="n"/>
+      <c r="AQ34" s="99" t="n"/>
+      <c r="AR34" s="99" t="n"/>
+      <c r="AS34" s="99" t="n"/>
+      <c r="AT34" s="99" t="n"/>
+      <c r="AU34" s="99" t="n"/>
+      <c r="AV34" s="99" t="n"/>
+      <c r="AW34" s="99" t="n"/>
+      <c r="AX34" s="99" t="n"/>
+      <c r="AY34" s="99" t="n"/>
+      <c r="AZ34" s="99" t="n"/>
+      <c r="BA34" s="99" t="n"/>
+      <c r="BB34" s="99" t="n"/>
+      <c r="BC34" s="99" t="n"/>
+      <c r="BD34" s="99" t="n"/>
+      <c r="BE34" s="47" t="n"/>
+      <c r="BF34" s="47" t="n"/>
+      <c r="BG34" s="47" t="n"/>
+      <c r="BH34" s="47" t="n"/>
     </row>
     <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="22" t="n"/>
-      <c r="B35" s="32" t="n"/>
-      <c r="C35" s="32" t="n"/>
-      <c r="D35" s="32" t="n"/>
-      <c r="E35" s="32" t="n"/>
-      <c r="F35" s="32" t="n"/>
-      <c r="G35" s="32" t="n"/>
-      <c r="H35" s="32" t="n"/>
-      <c r="I35" s="32" t="n"/>
-      <c r="J35" s="32" t="n"/>
-      <c r="K35" s="32" t="n"/>
-      <c r="L35" s="24" t="n"/>
+      <c r="A35" s="55" t="n"/>
+      <c r="B35" s="81" t="n"/>
+      <c r="C35" s="81" t="n"/>
+      <c r="D35" s="81" t="n"/>
+      <c r="E35" s="81" t="n"/>
+      <c r="F35" s="81" t="n"/>
+      <c r="G35" s="81" t="n"/>
+      <c r="H35" s="81" t="n"/>
+      <c r="I35" s="81" t="n"/>
+      <c r="J35" s="81" t="n"/>
+      <c r="K35" s="81" t="n"/>
+      <c r="L35" s="58" t="n"/>
+      <c r="M35" s="47" t="n"/>
+      <c r="N35" s="47" t="n"/>
+      <c r="O35" s="47" t="n"/>
+      <c r="P35" s="47" t="n"/>
+      <c r="Q35" s="47" t="n"/>
+      <c r="R35" s="47" t="n"/>
+      <c r="S35" s="47" t="n"/>
+      <c r="T35" s="47" t="n"/>
+      <c r="U35" s="47" t="n"/>
+      <c r="V35" s="47" t="n"/>
+      <c r="W35" s="47" t="n"/>
+      <c r="X35" s="47" t="n"/>
+      <c r="Y35" s="47" t="n"/>
+      <c r="Z35" s="47" t="n"/>
+      <c r="AA35" s="47" t="n"/>
+      <c r="AB35" s="47" t="n"/>
+      <c r="AC35" s="47" t="n"/>
+      <c r="AD35" s="47" t="n"/>
+      <c r="AE35" s="47" t="n"/>
+      <c r="AF35" s="47" t="n"/>
+      <c r="AG35" s="47" t="n"/>
+      <c r="AH35" s="47" t="n"/>
+      <c r="AI35" s="47" t="n"/>
+      <c r="AJ35" s="47" t="n"/>
+      <c r="AK35" s="47" t="n"/>
+      <c r="AL35" s="47" t="n"/>
+      <c r="AM35" s="47" t="n"/>
+      <c r="AN35" s="47" t="n"/>
+      <c r="AO35" s="47" t="n"/>
+      <c r="AP35" s="47" t="n"/>
+      <c r="AQ35" s="47" t="n"/>
+      <c r="AR35" s="47" t="n"/>
+      <c r="AS35" s="47" t="n"/>
+      <c r="AT35" s="47" t="n"/>
+      <c r="AU35" s="47" t="n"/>
+      <c r="AV35" s="47" t="n"/>
+      <c r="AW35" s="47" t="n"/>
+      <c r="AX35" s="47" t="n"/>
+      <c r="AY35" s="47" t="n"/>
+      <c r="AZ35" s="47" t="n"/>
+      <c r="BA35" s="47" t="n"/>
+      <c r="BB35" s="47" t="n"/>
+      <c r="BC35" s="47" t="n"/>
+      <c r="BD35" s="47" t="n"/>
+      <c r="BE35" s="47" t="n"/>
+      <c r="BF35" s="47" t="n"/>
+      <c r="BG35" s="47" t="n"/>
+      <c r="BH35" s="47" t="n"/>
     </row>
     <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="22" t="n"/>
-      <c r="B36" s="32" t="n"/>
-      <c r="C36" s="32" t="n"/>
-      <c r="D36" s="32" t="n"/>
-      <c r="E36" s="32" t="n"/>
-      <c r="F36" s="32" t="n"/>
-      <c r="G36" s="32" t="n"/>
-      <c r="H36" s="32" t="n"/>
-      <c r="I36" s="32" t="n"/>
-      <c r="J36" s="32" t="n"/>
-      <c r="K36" s="32" t="n"/>
-      <c r="L36" s="24" t="n"/>
+      <c r="A36" s="55" t="n"/>
+      <c r="B36" s="81" t="n"/>
+      <c r="C36" s="81" t="n"/>
+      <c r="D36" s="81" t="n"/>
+      <c r="E36" s="81" t="n"/>
+      <c r="F36" s="81" t="n"/>
+      <c r="G36" s="81" t="n"/>
+      <c r="H36" s="81" t="n"/>
+      <c r="I36" s="81" t="n"/>
+      <c r="J36" s="81" t="n"/>
+      <c r="K36" s="81" t="n"/>
+      <c r="L36" s="58" t="n"/>
+      <c r="M36" s="47" t="n"/>
+      <c r="N36" s="47" t="n"/>
+      <c r="O36" s="47" t="n"/>
+      <c r="P36" s="47" t="n"/>
+      <c r="Q36" s="47" t="n"/>
+      <c r="R36" s="47" t="n"/>
+      <c r="S36" s="47" t="n"/>
+      <c r="T36" s="47" t="n"/>
+      <c r="U36" s="47" t="n"/>
+      <c r="V36" s="47" t="n"/>
+      <c r="W36" s="47" t="n"/>
+      <c r="X36" s="47" t="n"/>
+      <c r="Y36" s="47" t="n"/>
+      <c r="Z36" s="47" t="n"/>
+      <c r="AA36" s="47" t="n"/>
+      <c r="AB36" s="47" t="n"/>
+      <c r="AC36" s="47" t="n"/>
+      <c r="AD36" s="47" t="n"/>
+      <c r="AE36" s="47" t="n"/>
+      <c r="AF36" s="47" t="n"/>
+      <c r="AG36" s="47" t="n"/>
+      <c r="AH36" s="47" t="n"/>
+      <c r="AI36" s="47" t="n"/>
+      <c r="AJ36" s="47" t="n"/>
+      <c r="AK36" s="47" t="n"/>
+      <c r="AL36" s="47" t="n"/>
+      <c r="AM36" s="47" t="n"/>
+      <c r="AN36" s="47" t="n"/>
+      <c r="AO36" s="47" t="n"/>
+      <c r="AP36" s="47" t="n"/>
+      <c r="AQ36" s="47" t="n"/>
+      <c r="AR36" s="47" t="n"/>
+      <c r="AS36" s="47" t="n"/>
+      <c r="AT36" s="47" t="n"/>
+      <c r="AU36" s="47" t="n"/>
+      <c r="AV36" s="47" t="n"/>
+      <c r="AW36" s="47" t="n"/>
+      <c r="AX36" s="47" t="n"/>
+      <c r="AY36" s="47" t="n"/>
+      <c r="AZ36" s="47" t="n"/>
+      <c r="BA36" s="47" t="n"/>
+      <c r="BB36" s="47" t="n"/>
+      <c r="BC36" s="47" t="n"/>
+      <c r="BD36" s="47" t="n"/>
+      <c r="BE36" s="47" t="n"/>
+      <c r="BF36" s="47" t="n"/>
+      <c r="BG36" s="47" t="n"/>
+      <c r="BH36" s="47" t="n"/>
     </row>
     <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="22" t="n"/>
-      <c r="B37" s="32" t="n"/>
-      <c r="C37" s="32" t="n"/>
-      <c r="D37" s="32" t="n"/>
-      <c r="E37" s="32" t="n"/>
-      <c r="F37" s="32" t="n"/>
-      <c r="G37" s="32" t="n"/>
-      <c r="H37" s="32" t="n"/>
-      <c r="I37" s="32" t="n"/>
-      <c r="J37" s="32" t="n"/>
-      <c r="K37" s="32" t="n"/>
-      <c r="L37" s="24" t="n"/>
+      <c r="A37" s="55" t="n"/>
+      <c r="B37" s="81" t="n"/>
+      <c r="C37" s="81" t="n"/>
+      <c r="D37" s="81" t="n"/>
+      <c r="E37" s="81" t="n"/>
+      <c r="F37" s="81" t="n"/>
+      <c r="G37" s="81" t="n"/>
+      <c r="H37" s="81" t="n"/>
+      <c r="I37" s="81" t="n"/>
+      <c r="J37" s="81" t="n"/>
+      <c r="K37" s="81" t="n"/>
+      <c r="L37" s="58" t="n"/>
+      <c r="M37" s="47" t="n"/>
+      <c r="N37" s="47" t="n"/>
+      <c r="O37" s="59" t="inlineStr">
+        <is>
+          <t>⑪</t>
+        </is>
+      </c>
+      <c r="P37" s="100" t="inlineStr">
+        <is>
+          <t>⑪削除（未実装・今後対応。無効化で代替）</t>
+        </is>
+      </c>
+      <c r="Q37" s="101" t="n"/>
+      <c r="R37" s="101" t="n"/>
+      <c r="S37" s="101" t="n"/>
+      <c r="T37" s="101" t="n"/>
+      <c r="U37" s="101" t="n"/>
+      <c r="V37" s="101" t="n"/>
+      <c r="W37" s="101" t="n"/>
+      <c r="X37" s="101" t="n"/>
+      <c r="Y37" s="101" t="n"/>
+      <c r="Z37" s="101" t="n"/>
+      <c r="AA37" s="101" t="n"/>
+      <c r="AB37" s="101" t="n"/>
+      <c r="AC37" s="101" t="n"/>
+      <c r="AD37" s="101" t="n"/>
+      <c r="AE37" s="101" t="n"/>
+      <c r="AF37" s="101" t="n"/>
+      <c r="AG37" s="101" t="n"/>
+      <c r="AH37" s="101" t="n"/>
+      <c r="AI37" s="101" t="n"/>
+      <c r="AJ37" s="101" t="n"/>
+      <c r="AK37" s="101" t="n"/>
+      <c r="AL37" s="101" t="n"/>
+      <c r="AM37" s="101" t="n"/>
+      <c r="AN37" s="101" t="n"/>
+      <c r="AO37" s="101" t="n"/>
+      <c r="AP37" s="101" t="n"/>
+      <c r="AQ37" s="101" t="n"/>
+      <c r="AR37" s="101" t="n"/>
+      <c r="AS37" s="101" t="n"/>
+      <c r="AT37" s="101" t="n"/>
+      <c r="AU37" s="101" t="n"/>
+      <c r="AV37" s="101" t="n"/>
+      <c r="AW37" s="101" t="n"/>
+      <c r="AX37" s="101" t="n"/>
+      <c r="AY37" s="101" t="n"/>
+      <c r="AZ37" s="101" t="n"/>
+      <c r="BA37" s="101" t="n"/>
+      <c r="BB37" s="101" t="n"/>
+      <c r="BC37" s="101" t="n"/>
+      <c r="BD37" s="102" t="n"/>
+      <c r="BE37" s="47" t="n"/>
+      <c r="BF37" s="47" t="n"/>
+      <c r="BG37" s="47" t="n"/>
+      <c r="BH37" s="47" t="n"/>
     </row>
     <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="35" t="n"/>
-      <c r="B38" s="36" t="n"/>
-      <c r="C38" s="36" t="n"/>
-      <c r="D38" s="36" t="n"/>
-      <c r="E38" s="36" t="n"/>
-      <c r="F38" s="36" t="n"/>
-      <c r="G38" s="36" t="n"/>
-      <c r="H38" s="36" t="n"/>
-      <c r="I38" s="36" t="n"/>
-      <c r="J38" s="36" t="n"/>
-      <c r="K38" s="36" t="n"/>
-      <c r="L38" s="37" t="n"/>
-    </row>
-    <row r="39" ht="17" customHeight="1"/>
-    <row r="40" ht="17" customHeight="1"/>
+      <c r="A38" s="55" t="n"/>
+      <c r="B38" s="81" t="n"/>
+      <c r="C38" s="81" t="n"/>
+      <c r="D38" s="81" t="n"/>
+      <c r="E38" s="81" t="n"/>
+      <c r="F38" s="81" t="n"/>
+      <c r="G38" s="81" t="n"/>
+      <c r="H38" s="81" t="n"/>
+      <c r="I38" s="81" t="n"/>
+      <c r="J38" s="81" t="n"/>
+      <c r="K38" s="81" t="n"/>
+      <c r="L38" s="58" t="n"/>
+      <c r="M38" s="47" t="n"/>
+      <c r="N38" s="47" t="n"/>
+      <c r="O38" s="47" t="n"/>
+      <c r="P38" s="103" t="n"/>
+      <c r="Q38" s="104" t="n"/>
+      <c r="R38" s="104" t="n"/>
+      <c r="S38" s="104" t="n"/>
+      <c r="T38" s="104" t="n"/>
+      <c r="U38" s="104" t="n"/>
+      <c r="V38" s="104" t="n"/>
+      <c r="W38" s="104" t="n"/>
+      <c r="X38" s="104" t="n"/>
+      <c r="Y38" s="104" t="n"/>
+      <c r="Z38" s="104" t="n"/>
+      <c r="AA38" s="104" t="n"/>
+      <c r="AB38" s="104" t="n"/>
+      <c r="AC38" s="104" t="n"/>
+      <c r="AD38" s="104" t="n"/>
+      <c r="AE38" s="104" t="n"/>
+      <c r="AF38" s="104" t="n"/>
+      <c r="AG38" s="104" t="n"/>
+      <c r="AH38" s="104" t="n"/>
+      <c r="AI38" s="104" t="n"/>
+      <c r="AJ38" s="104" t="n"/>
+      <c r="AK38" s="104" t="n"/>
+      <c r="AL38" s="104" t="n"/>
+      <c r="AM38" s="104" t="n"/>
+      <c r="AN38" s="104" t="n"/>
+      <c r="AO38" s="104" t="n"/>
+      <c r="AP38" s="104" t="n"/>
+      <c r="AQ38" s="104" t="n"/>
+      <c r="AR38" s="104" t="n"/>
+      <c r="AS38" s="104" t="n"/>
+      <c r="AT38" s="104" t="n"/>
+      <c r="AU38" s="104" t="n"/>
+      <c r="AV38" s="104" t="n"/>
+      <c r="AW38" s="104" t="n"/>
+      <c r="AX38" s="104" t="n"/>
+      <c r="AY38" s="104" t="n"/>
+      <c r="AZ38" s="104" t="n"/>
+      <c r="BA38" s="104" t="n"/>
+      <c r="BB38" s="104" t="n"/>
+      <c r="BC38" s="104" t="n"/>
+      <c r="BD38" s="105" t="n"/>
+      <c r="BE38" s="47" t="n"/>
+      <c r="BF38" s="47" t="n"/>
+      <c r="BG38" s="47" t="n"/>
+      <c r="BH38" s="47" t="n"/>
+    </row>
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="55" t="n"/>
+      <c r="B39" s="81" t="n"/>
+      <c r="C39" s="81" t="n"/>
+      <c r="D39" s="81" t="n"/>
+      <c r="E39" s="81" t="n"/>
+      <c r="F39" s="81" t="n"/>
+      <c r="G39" s="81" t="n"/>
+      <c r="H39" s="81" t="n"/>
+      <c r="I39" s="81" t="n"/>
+      <c r="J39" s="81" t="n"/>
+      <c r="K39" s="81" t="n"/>
+      <c r="L39" s="58" t="n"/>
+      <c r="M39" s="47" t="n"/>
+      <c r="N39" s="47" t="n"/>
+      <c r="O39" s="47" t="n"/>
+      <c r="P39" s="47" t="n"/>
+      <c r="Q39" s="47" t="n"/>
+      <c r="R39" s="47" t="n"/>
+      <c r="S39" s="47" t="n"/>
+      <c r="T39" s="47" t="n"/>
+      <c r="U39" s="47" t="n"/>
+      <c r="V39" s="47" t="n"/>
+      <c r="W39" s="47" t="n"/>
+      <c r="X39" s="47" t="n"/>
+      <c r="Y39" s="47" t="n"/>
+      <c r="Z39" s="47" t="n"/>
+      <c r="AA39" s="47" t="n"/>
+      <c r="AB39" s="47" t="n"/>
+      <c r="AC39" s="47" t="n"/>
+      <c r="AD39" s="47" t="n"/>
+      <c r="AE39" s="47" t="n"/>
+      <c r="AF39" s="47" t="n"/>
+      <c r="AG39" s="47" t="n"/>
+      <c r="AH39" s="47" t="n"/>
+      <c r="AI39" s="47" t="n"/>
+      <c r="AJ39" s="47" t="n"/>
+      <c r="AK39" s="47" t="n"/>
+      <c r="AL39" s="47" t="n"/>
+      <c r="AM39" s="47" t="n"/>
+      <c r="AN39" s="47" t="n"/>
+      <c r="AO39" s="47" t="n"/>
+      <c r="AP39" s="47" t="n"/>
+      <c r="AQ39" s="47" t="n"/>
+      <c r="AR39" s="47" t="n"/>
+      <c r="AS39" s="47" t="n"/>
+      <c r="AT39" s="47" t="n"/>
+      <c r="AU39" s="47" t="n"/>
+      <c r="AV39" s="47" t="n"/>
+      <c r="AW39" s="47" t="n"/>
+      <c r="AX39" s="47" t="n"/>
+      <c r="AY39" s="47" t="n"/>
+      <c r="AZ39" s="47" t="n"/>
+      <c r="BA39" s="47" t="n"/>
+      <c r="BB39" s="47" t="n"/>
+      <c r="BC39" s="47" t="n"/>
+      <c r="BD39" s="47" t="n"/>
+      <c r="BE39" s="47" t="n"/>
+      <c r="BF39" s="47" t="n"/>
+      <c r="BG39" s="47" t="n"/>
+      <c r="BH39" s="47" t="n"/>
+    </row>
+    <row r="40" ht="17" customHeight="1">
+      <c r="A40" s="55" t="n"/>
+      <c r="B40" s="81" t="n"/>
+      <c r="C40" s="81" t="n"/>
+      <c r="D40" s="81" t="n"/>
+      <c r="E40" s="81" t="n"/>
+      <c r="F40" s="81" t="n"/>
+      <c r="G40" s="81" t="n"/>
+      <c r="H40" s="81" t="n"/>
+      <c r="I40" s="81" t="n"/>
+      <c r="J40" s="81" t="n"/>
+      <c r="K40" s="81" t="n"/>
+      <c r="L40" s="58" t="n"/>
+      <c r="M40" s="47" t="n"/>
+      <c r="N40" s="47" t="n"/>
+      <c r="O40" s="47" t="n"/>
+      <c r="P40" s="47" t="n"/>
+      <c r="Q40" s="47" t="n"/>
+      <c r="R40" s="47" t="n"/>
+      <c r="S40" s="47" t="n"/>
+      <c r="T40" s="47" t="n"/>
+      <c r="U40" s="47" t="n"/>
+      <c r="V40" s="47" t="n"/>
+      <c r="W40" s="47" t="n"/>
+      <c r="X40" s="47" t="n"/>
+      <c r="Y40" s="47" t="n"/>
+      <c r="Z40" s="47" t="n"/>
+      <c r="AA40" s="47" t="n"/>
+      <c r="AB40" s="47" t="n"/>
+      <c r="AC40" s="47" t="n"/>
+      <c r="AD40" s="47" t="n"/>
+      <c r="AE40" s="47" t="n"/>
+      <c r="AF40" s="47" t="n"/>
+      <c r="AG40" s="47" t="n"/>
+      <c r="AH40" s="47" t="n"/>
+      <c r="AI40" s="47" t="n"/>
+      <c r="AJ40" s="47" t="n"/>
+      <c r="AK40" s="47" t="n"/>
+      <c r="AL40" s="47" t="n"/>
+      <c r="AM40" s="47" t="n"/>
+      <c r="AN40" s="47" t="n"/>
+      <c r="AO40" s="47" t="n"/>
+      <c r="AP40" s="47" t="n"/>
+      <c r="AQ40" s="47" t="n"/>
+      <c r="AR40" s="47" t="n"/>
+      <c r="AS40" s="47" t="n"/>
+      <c r="AT40" s="47" t="n"/>
+      <c r="AU40" s="47" t="n"/>
+      <c r="AV40" s="47" t="n"/>
+      <c r="AW40" s="47" t="n"/>
+      <c r="AX40" s="47" t="n"/>
+      <c r="AY40" s="47" t="n"/>
+      <c r="AZ40" s="47" t="n"/>
+      <c r="BA40" s="47" t="n"/>
+      <c r="BB40" s="47" t="n"/>
+      <c r="BC40" s="47" t="n"/>
+      <c r="BD40" s="47" t="n"/>
+      <c r="BE40" s="47" t="n"/>
+      <c r="BF40" s="47" t="n"/>
+      <c r="BG40" s="47" t="n"/>
+      <c r="BH40" s="47" t="n"/>
+    </row>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" s="55" t="n"/>
+      <c r="B41" s="81" t="n"/>
+      <c r="C41" s="81" t="n"/>
+      <c r="D41" s="81" t="n"/>
+      <c r="E41" s="81" t="n"/>
+      <c r="F41" s="81" t="n"/>
+      <c r="G41" s="81" t="n"/>
+      <c r="H41" s="81" t="n"/>
+      <c r="I41" s="81" t="n"/>
+      <c r="J41" s="81" t="n"/>
+      <c r="K41" s="81" t="n"/>
+      <c r="L41" s="58" t="n"/>
+      <c r="M41" s="47" t="n"/>
+      <c r="N41" s="47" t="n"/>
+      <c r="O41" s="47" t="n"/>
+      <c r="P41" s="47" t="n"/>
+      <c r="Q41" s="47" t="n"/>
+      <c r="R41" s="47" t="n"/>
+      <c r="S41" s="47" t="n"/>
+      <c r="T41" s="47" t="n"/>
+      <c r="U41" s="47" t="n"/>
+      <c r="V41" s="47" t="n"/>
+      <c r="W41" s="47" t="n"/>
+      <c r="X41" s="47" t="n"/>
+      <c r="Y41" s="47" t="n"/>
+      <c r="Z41" s="47" t="n"/>
+      <c r="AA41" s="47" t="n"/>
+      <c r="AB41" s="47" t="n"/>
+      <c r="AC41" s="47" t="n"/>
+      <c r="AD41" s="47" t="n"/>
+      <c r="AE41" s="47" t="n"/>
+      <c r="AF41" s="47" t="n"/>
+      <c r="AG41" s="47" t="n"/>
+      <c r="AH41" s="47" t="n"/>
+      <c r="AI41" s="47" t="n"/>
+      <c r="AJ41" s="47" t="n"/>
+      <c r="AK41" s="47" t="n"/>
+      <c r="AL41" s="47" t="n"/>
+      <c r="AM41" s="47" t="n"/>
+      <c r="AN41" s="47" t="n"/>
+      <c r="AO41" s="47" t="n"/>
+      <c r="AP41" s="47" t="n"/>
+      <c r="AQ41" s="47" t="n"/>
+      <c r="AR41" s="47" t="n"/>
+      <c r="AS41" s="47" t="n"/>
+      <c r="AT41" s="47" t="n"/>
+      <c r="AU41" s="47" t="n"/>
+      <c r="AV41" s="47" t="n"/>
+      <c r="AW41" s="47" t="n"/>
+      <c r="AX41" s="47" t="n"/>
+      <c r="AY41" s="47" t="n"/>
+      <c r="AZ41" s="47" t="n"/>
+      <c r="BA41" s="47" t="n"/>
+      <c r="BB41" s="47" t="n"/>
+      <c r="BC41" s="47" t="n"/>
+      <c r="BD41" s="47" t="n"/>
+      <c r="BE41" s="47" t="n"/>
+      <c r="BF41" s="47" t="n"/>
+      <c r="BG41" s="47" t="n"/>
+      <c r="BH41" s="47" t="n"/>
+    </row>
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="106" t="n"/>
+      <c r="B42" s="107" t="n"/>
+      <c r="C42" s="107" t="n"/>
+      <c r="D42" s="107" t="n"/>
+      <c r="E42" s="107" t="n"/>
+      <c r="F42" s="107" t="n"/>
+      <c r="G42" s="107" t="n"/>
+      <c r="H42" s="107" t="n"/>
+      <c r="I42" s="107" t="n"/>
+      <c r="J42" s="107" t="n"/>
+      <c r="K42" s="107" t="n"/>
+      <c r="L42" s="108" t="n"/>
+      <c r="M42" s="47" t="n"/>
+      <c r="N42" s="47" t="n"/>
+      <c r="O42" s="47" t="n"/>
+      <c r="P42" s="47" t="n"/>
+      <c r="Q42" s="47" t="n"/>
+      <c r="R42" s="47" t="n"/>
+      <c r="S42" s="47" t="n"/>
+      <c r="T42" s="47" t="n"/>
+      <c r="U42" s="47" t="n"/>
+      <c r="V42" s="47" t="n"/>
+      <c r="W42" s="47" t="n"/>
+      <c r="X42" s="47" t="n"/>
+      <c r="Y42" s="47" t="n"/>
+      <c r="Z42" s="47" t="n"/>
+      <c r="AA42" s="47" t="n"/>
+      <c r="AB42" s="47" t="n"/>
+      <c r="AC42" s="47" t="n"/>
+      <c r="AD42" s="47" t="n"/>
+      <c r="AE42" s="47" t="n"/>
+      <c r="AF42" s="47" t="n"/>
+      <c r="AG42" s="47" t="n"/>
+      <c r="AH42" s="47" t="n"/>
+      <c r="AI42" s="47" t="n"/>
+      <c r="AJ42" s="47" t="n"/>
+      <c r="AK42" s="47" t="n"/>
+      <c r="AL42" s="47" t="n"/>
+      <c r="AM42" s="47" t="n"/>
+      <c r="AN42" s="47" t="n"/>
+      <c r="AO42" s="47" t="n"/>
+      <c r="AP42" s="47" t="n"/>
+      <c r="AQ42" s="47" t="n"/>
+      <c r="AR42" s="47" t="n"/>
+      <c r="AS42" s="47" t="n"/>
+      <c r="AT42" s="47" t="n"/>
+      <c r="AU42" s="47" t="n"/>
+      <c r="AV42" s="47" t="n"/>
+      <c r="AW42" s="47" t="n"/>
+      <c r="AX42" s="47" t="n"/>
+      <c r="AY42" s="47" t="n"/>
+      <c r="AZ42" s="47" t="n"/>
+      <c r="BA42" s="47" t="n"/>
+      <c r="BB42" s="47" t="n"/>
+      <c r="BC42" s="47" t="n"/>
+      <c r="BD42" s="47" t="n"/>
+      <c r="BE42" s="47" t="n"/>
+      <c r="BF42" s="47" t="n"/>
+      <c r="BG42" s="47" t="n"/>
+      <c r="BH42" s="47" t="n"/>
+    </row>
+    <row r="43" ht="17" customHeight="1"/>
+    <row r="44" ht="17" customHeight="1"/>
   </sheetData>
-  <mergeCells count="38">
-    <mergeCell ref="V15:AR16"/>
-    <mergeCell ref="AD9:AK9"/>
-    <mergeCell ref="AL9:AS9"/>
-    <mergeCell ref="AD8:AK8"/>
-    <mergeCell ref="AR1:BH3"/>
-    <mergeCell ref="B12:K13"/>
-    <mergeCell ref="B8:K9"/>
-    <mergeCell ref="AC30:AN32"/>
-    <mergeCell ref="V8:AC8"/>
-    <mergeCell ref="B14:K15"/>
-    <mergeCell ref="AT8:BD8"/>
-    <mergeCell ref="N24:U25"/>
-    <mergeCell ref="V10:AC10"/>
-    <mergeCell ref="N15:U16"/>
-    <mergeCell ref="AD10:AK10"/>
-    <mergeCell ref="V27:AN28"/>
-    <mergeCell ref="V9:AC9"/>
-    <mergeCell ref="N27:U28"/>
-    <mergeCell ref="B10:K11"/>
-    <mergeCell ref="V24:AN25"/>
-    <mergeCell ref="V12:AR13"/>
-    <mergeCell ref="N8:U8"/>
-    <mergeCell ref="B6:K7"/>
-    <mergeCell ref="V21:AR22"/>
-    <mergeCell ref="AT10:BD10"/>
-    <mergeCell ref="N10:U10"/>
-    <mergeCell ref="N30:Y32"/>
-    <mergeCell ref="A1:AQ3"/>
-    <mergeCell ref="N5:AN6"/>
-    <mergeCell ref="AL8:AS8"/>
-    <mergeCell ref="N9:U9"/>
-    <mergeCell ref="AT9:BD9"/>
-    <mergeCell ref="V18:AX19"/>
-    <mergeCell ref="N18:U19"/>
-    <mergeCell ref="N12:U13"/>
-    <mergeCell ref="N21:U22"/>
-    <mergeCell ref="AL10:AS10"/>
-    <mergeCell ref="B16:K17"/>
+  <mergeCells count="67">
+    <mergeCell ref="B13:I14"/>
+    <mergeCell ref="U11:AF11"/>
+    <mergeCell ref="B27:K28"/>
+    <mergeCell ref="AG30:AJ30"/>
+    <mergeCell ref="B6:K6"/>
+    <mergeCell ref="B20:K20"/>
+    <mergeCell ref="B11:K12"/>
+    <mergeCell ref="AK29:AP29"/>
+    <mergeCell ref="W29:AF29"/>
+    <mergeCell ref="B29:K30"/>
+    <mergeCell ref="A1:N3"/>
+    <mergeCell ref="AQ29:AS29"/>
+    <mergeCell ref="B23:K24"/>
+    <mergeCell ref="AV5:BF6"/>
+    <mergeCell ref="AX28:AZ28"/>
+    <mergeCell ref="W13:AF13"/>
+    <mergeCell ref="AP11:BA11"/>
+    <mergeCell ref="AL1:AU3"/>
+    <mergeCell ref="AX30:AZ30"/>
+    <mergeCell ref="W15:AF15"/>
+    <mergeCell ref="BB2:BG2"/>
+    <mergeCell ref="W30:AF30"/>
+    <mergeCell ref="AG27:AJ27"/>
+    <mergeCell ref="AV1:BA3"/>
+    <mergeCell ref="AJ11:AO11"/>
+    <mergeCell ref="AK28:AP28"/>
+    <mergeCell ref="AR13:BA13"/>
+    <mergeCell ref="AX27:AZ27"/>
+    <mergeCell ref="B25:K26"/>
+    <mergeCell ref="AH1:AK3"/>
+    <mergeCell ref="O13:V13"/>
+    <mergeCell ref="B21:K22"/>
+    <mergeCell ref="AK30:AP30"/>
+    <mergeCell ref="AR15:BA15"/>
+    <mergeCell ref="W27:AF27"/>
+    <mergeCell ref="N5:AD6"/>
+    <mergeCell ref="O28:V28"/>
+    <mergeCell ref="O15:V15"/>
+    <mergeCell ref="B17:K18"/>
+    <mergeCell ref="AT30:AW30"/>
+    <mergeCell ref="P19:Z20"/>
+    <mergeCell ref="O30:V30"/>
+    <mergeCell ref="AB19:AL20"/>
+    <mergeCell ref="W28:AF28"/>
+    <mergeCell ref="AQ28:AS28"/>
+    <mergeCell ref="O29:V29"/>
+    <mergeCell ref="AG29:AJ29"/>
+    <mergeCell ref="B16:K16"/>
+    <mergeCell ref="O11:T11"/>
+    <mergeCell ref="AT28:AW28"/>
+    <mergeCell ref="P34:BD34"/>
+    <mergeCell ref="AJ13:AQ13"/>
+    <mergeCell ref="AT27:AW27"/>
+    <mergeCell ref="AX29:AZ29"/>
+    <mergeCell ref="P37:BD38"/>
+    <mergeCell ref="B9:K10"/>
+    <mergeCell ref="AK27:AP27"/>
+    <mergeCell ref="AQ27:AS27"/>
+    <mergeCell ref="AJ15:AQ15"/>
+    <mergeCell ref="O27:V27"/>
+    <mergeCell ref="AQ30:AS30"/>
+    <mergeCell ref="P17:BD17"/>
+    <mergeCell ref="J13:K14"/>
+    <mergeCell ref="AT29:AW29"/>
+    <mergeCell ref="B7:K8"/>
+    <mergeCell ref="P9:AD9"/>
+    <mergeCell ref="AG28:AJ28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2292,7 +4610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2353,17 +4671,17 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>休暇種別一覧</t>
+          <t>新規登録ボタン</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>一覧</t>
+          <t>ボタン</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>出力</t>
+          <t>入力</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
@@ -2371,11 +4689,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr"/>
-      <c r="G2" s="8" t="inlineStr"/>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="H2" s="8" t="inlineStr">
         <is>
-          <t>列：名称、法的根拠、有給、日数ルール、有効。</t>
+          <t>見出し右。フォームを開く</t>
         </is>
       </c>
     </row>
@@ -2385,31 +4711,39 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>休暇種別一覧</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>テキスト</t>
+          <t>一覧</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>入力</t>
+          <t>出力</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>最大100文字</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr"/>
-      <c r="H3" s="8" t="inlineStr"/>
+          <t>列：名称、法的根拠（なしは「—」）、有給・無給、日数ルール（上限あり／上限なし）、半日取得（可／不可）、有効・無効（バッジ）、操作［編集］</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>0件は「休暇種別が登録されていません。」</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">
@@ -2417,7 +4751,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>法的根拠</t>
+          <t>名称</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
@@ -2432,7 +4766,7 @@
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
@@ -2440,8 +4774,16 @@
           <t>最大100文字</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr"/>
-      <c r="H4" s="8" t="inlineStr"/>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>重複不可</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
@@ -2449,12 +4791,12 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>有給・無給</t>
+          <t>法的根拠</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>ラジオ</t>
+          <t>テキスト</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -2464,12 +4806,24 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="8" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>最大100文字</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>プレースホルダ「例：労働基準法第39条」</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
@@ -2477,7 +4831,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>日数ルール</t>
+          <t>有給・無給</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -2492,16 +4846,20 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="8" t="inlineStr"/>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>上限付き／無制限</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>有給／無給</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>有給</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n">
@@ -2509,12 +4867,12 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>半日取得可</t>
+          <t>日数ルール</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>チェックボックス</t>
+          <t>プルダウン</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -2527,9 +4885,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr"/>
-      <c r="G7" s="8" t="inlineStr"/>
-      <c r="H7" s="8" t="inlineStr"/>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>上限あり／上限なし</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>上限あり</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>上限ありの種別のみ付与・残日数管理の対象（SCR-305・SCR-107）</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
@@ -2537,12 +4907,12 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>有効</t>
+          <t>半日取得</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>チェックボックス</t>
+          <t>プルダウン</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -2555,8 +4925,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr"/>
-      <c r="G8" s="8" t="inlineStr"/>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>可／不可</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
       <c r="H8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -2565,12 +4943,12 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>新規</t>
+          <t>有効・無効</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>ボタン</t>
+          <t>プルダウン</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -2583,9 +4961,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr"/>
-      <c r="G9" s="8" t="inlineStr"/>
-      <c r="H9" s="8" t="inlineStr"/>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>有効／無効</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>有効</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>無効にすると申請の選択肢に出ない</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
@@ -2593,7 +4983,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>保存</t>
+          <t>登録する／更新する／キャンセル</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -2611,9 +5001,101 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr"/>
-      <c r="G10" s="8" t="inlineStr"/>
-      <c r="H10" s="8" t="inlineStr"/>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>処理中は非活性</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>完了・エラーメッセージ</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>アラート</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>出力</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>「休暇種別「{名称}」を登録しました。」／「…を更新しました。」</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>非表示</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>緑（完了）／赤（エラー）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="109" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="109" t="inlineStr">
+        <is>
+          <t>休暇種別の削除</t>
+        </is>
+      </c>
+      <c r="C12" s="109" t="inlineStr">
+        <is>
+          <t>ボタン</t>
+        </is>
+      </c>
+      <c r="D12" s="109" t="inlineStr">
+        <is>
+          <t>入力</t>
+        </is>
+      </c>
+      <c r="E12" s="109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" s="109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" s="109" t="inlineStr">
+        <is>
+          <t>【未実装（今後対応）】削除機能は無い（無効化で代替）</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2627,7 +5109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2670,12 +5152,12 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>新規ボタン押下</t>
+          <t>画面表示</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>入力欄を空にして新規登録モードにする</t>
+          <t>GET /api/admin/leave-types で一覧を取得する</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
@@ -2691,12 +5173,12 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>保存ボタン押下</t>
+          <t>新規登録ボタン押下</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>休暇種別を登録または更新する</t>
+          <t>空の登録フォームを開く</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
@@ -2705,6 +5187,52 @@
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>編集ボタン押下</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>行の内容を入れた編集フォームを開く（一覧のデータを使う。再取得はしない）</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>SCR-303</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>登録する／更新する押下</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>名称の必須チェック後、POST または PUT /api/admin/leave-types/{id}。成功時はフォームを閉じ、一覧を再取得して完了メッセージを表示</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>SCR-303</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>E-013／E-015／E-016</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2718,13 +5246,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="56" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2760,12 +5288,72 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>必須・重複不可</t>
+          <t>必須（画面側）</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>E-002 / E-005</t>
+          <t>名称は必須入力です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>重複不可（API）</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>E-013「名称は既に登録されています。」</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>年次有給休暇の編集</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>名称・有給区分・日数ルール・有効フラグは変更不可（API）</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>E-016「年次有給休暇の名称・有給区分・日数ルール・有効フラグは固定のため、この操作は行えません。」</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>対象データ</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>存在すること</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>E-015「対象のデータが見つかりません。」</t>
         </is>
       </c>
     </row>
